--- a/research/traditional_assets/database/data/hong_kong/hong_kong_semiconductor_equip.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_semiconductor_equip.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1467937038659387</v>
+        <v>0.1465890692545599</v>
       </c>
       <c r="C2">
-        <v>20.42455760322572</v>
+        <v>20.24617539948147</v>
       </c>
       <c r="D2">
-        <v>16.11455760322572</v>
+        <v>16.14727539948147</v>
       </c>
       <c r="E2">
-        <v>-9.41</v>
+        <v>-9.1989</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.2111</v>
       </c>
       <c r="G2">
         <v>4.31</v>
@@ -1445,28 +1445,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.01061833</v>
       </c>
       <c r="N2">
-        <v>1.783333333333333</v>
+        <v>1.772715003333333</v>
       </c>
       <c r="O2">
-        <v>0.29425</v>
+        <v>0.29249797555</v>
       </c>
       <c r="P2">
-        <v>1.489083333333333</v>
+        <v>1.480217027783334</v>
       </c>
       <c r="Q2">
-        <v>2.639083333333334</v>
+        <v>2.630217027783334</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1467937038659387</v>
+        <v>0.1476455194490504</v>
       </c>
       <c r="T2">
-        <v>1.968555267829298</v>
+        <v>1.985158739027656</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>167.9485694391993</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1465890692545599</v>
+        <v>0.1463844346431811</v>
       </c>
       <c r="C3">
-        <v>20.24617539948147</v>
+        <v>20.06792632157415</v>
       </c>
       <c r="D3">
-        <v>16.14727539948147</v>
+        <v>16.18012632157415</v>
       </c>
       <c r="E3">
-        <v>-9.1989</v>
+        <v>-8.9878</v>
       </c>
       <c r="F3">
-        <v>0.2111</v>
+        <v>0.4222</v>
       </c>
       <c r="G3">
         <v>4.31</v>
@@ -1527,28 +1527,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M3">
-        <v>0.01061833</v>
+        <v>0.02123666</v>
       </c>
       <c r="N3">
-        <v>1.772715003333333</v>
+        <v>1.762096673333333</v>
       </c>
       <c r="O3">
-        <v>0.29249797555</v>
+        <v>0.2907459511</v>
       </c>
       <c r="P3">
-        <v>1.480217027783334</v>
+        <v>1.471350722233333</v>
       </c>
       <c r="Q3">
-        <v>2.630217027783334</v>
+        <v>2.621350722233333</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1476455194490504</v>
+        <v>0.1485147190236542</v>
       </c>
       <c r="T3">
-        <v>1.985158739027656</v>
+        <v>2.002101056577001</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>167.9485694391993</v>
+        <v>83.97428471959967</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1463844346431811</v>
+        <v>0.1461798000318023</v>
       </c>
       <c r="C4">
-        <v>20.06792632157415</v>
+        <v>19.88981118367614</v>
       </c>
       <c r="D4">
-        <v>16.18012632157415</v>
+        <v>16.21311118367614</v>
       </c>
       <c r="E4">
-        <v>-8.9878</v>
+        <v>-8.7767</v>
       </c>
       <c r="F4">
-        <v>0.4222</v>
+        <v>0.6333</v>
       </c>
       <c r="G4">
         <v>4.31</v>
@@ -1609,28 +1609,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M4">
-        <v>0.02123666</v>
+        <v>0.03185499</v>
       </c>
       <c r="N4">
-        <v>1.762096673333333</v>
+        <v>1.751478343333333</v>
       </c>
       <c r="O4">
-        <v>0.2907459511</v>
+        <v>0.28899392665</v>
       </c>
       <c r="P4">
-        <v>1.471350722233333</v>
+        <v>1.462484416683334</v>
       </c>
       <c r="Q4">
-        <v>2.621350722233333</v>
+        <v>2.612484416683333</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1485147190236542</v>
+        <v>0.1494018402389715</v>
       </c>
       <c r="T4">
-        <v>2.002101056577001</v>
+        <v>2.019392700261385</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>83.97428471959967</v>
+        <v>55.98285647973311</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1461798000318023</v>
+        <v>0.1459751654204235</v>
       </c>
       <c r="C5">
-        <v>19.88981118367614</v>
+        <v>19.71183080661251</v>
       </c>
       <c r="D5">
-        <v>16.21311118367614</v>
+        <v>16.24623080661251</v>
       </c>
       <c r="E5">
-        <v>-8.7767</v>
+        <v>-8.5656</v>
       </c>
       <c r="F5">
-        <v>0.6333</v>
+        <v>0.8444</v>
       </c>
       <c r="G5">
         <v>4.31</v>
@@ -1691,28 +1691,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M5">
-        <v>0.03185499</v>
+        <v>0.04247332</v>
       </c>
       <c r="N5">
-        <v>1.751478343333333</v>
+        <v>1.740860013333333</v>
       </c>
       <c r="O5">
-        <v>0.28899392665</v>
+        <v>0.2872419022</v>
       </c>
       <c r="P5">
-        <v>1.462484416683334</v>
+        <v>1.453618111133333</v>
       </c>
       <c r="Q5">
-        <v>2.612484416683333</v>
+        <v>2.603618111133334</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1494018402389715</v>
+        <v>0.1503074431462745</v>
       </c>
       <c r="T5">
-        <v>2.019392700261385</v>
+        <v>2.037044586522526</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>55.98285647973311</v>
+        <v>41.98714235979983</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1459751654204235</v>
+        <v>0.1457705308090447</v>
       </c>
       <c r="C6">
-        <v>19.71183080661251</v>
+        <v>19.53398601792905</v>
       </c>
       <c r="D6">
-        <v>16.24623080661251</v>
+        <v>16.27948601792905</v>
       </c>
       <c r="E6">
-        <v>-8.5656</v>
+        <v>-8.3545</v>
       </c>
       <c r="F6">
-        <v>0.8444</v>
+        <v>1.0555</v>
       </c>
       <c r="G6">
         <v>4.31</v>
@@ -1773,28 +1773,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M6">
-        <v>0.04247332</v>
+        <v>0.05309165</v>
       </c>
       <c r="N6">
-        <v>1.740860013333333</v>
+        <v>1.730241683333333</v>
       </c>
       <c r="O6">
-        <v>0.2872419022</v>
+        <v>0.28548987775</v>
       </c>
       <c r="P6">
-        <v>1.453618111133333</v>
+        <v>1.444751805583333</v>
       </c>
       <c r="Q6">
-        <v>2.603618111133334</v>
+        <v>2.594751805583334</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1503074431462745</v>
+        <v>0.1512321113779418</v>
       </c>
       <c r="T6">
-        <v>2.037044586522526</v>
+        <v>2.055068091441796</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>41.98714235979983</v>
+        <v>33.58971388783986</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1457705308090447</v>
+        <v>0.1455658961976659</v>
       </c>
       <c r="C7">
-        <v>19.53398601792905</v>
+        <v>19.35627765196124</v>
       </c>
       <c r="D7">
-        <v>16.27948601792905</v>
+        <v>16.31287765196124</v>
       </c>
       <c r="E7">
-        <v>-8.3545</v>
+        <v>-8.1434</v>
       </c>
       <c r="F7">
-        <v>1.0555</v>
+        <v>1.2666</v>
       </c>
       <c r="G7">
         <v>4.31</v>
@@ -1855,28 +1855,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M7">
-        <v>0.05309165</v>
+        <v>0.06370998</v>
       </c>
       <c r="N7">
-        <v>1.730241683333333</v>
+        <v>1.719623353333333</v>
       </c>
       <c r="O7">
-        <v>0.28548987775</v>
+        <v>0.2837378533</v>
       </c>
       <c r="P7">
-        <v>1.444751805583333</v>
+        <v>1.435885500033333</v>
       </c>
       <c r="Q7">
-        <v>2.594751805583334</v>
+        <v>2.585885500033333</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1512321113779418</v>
+        <v>0.1521764534017722</v>
       </c>
       <c r="T7">
-        <v>2.055068091441796</v>
+        <v>2.073475075189136</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>33.58971388783986</v>
+        <v>27.99142823986655</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1455658961976659</v>
+        <v>0.1453612615862871</v>
       </c>
       <c r="C8">
-        <v>19.35627765196124</v>
+        <v>19.178706549904</v>
       </c>
       <c r="D8">
-        <v>16.31287765196124</v>
+        <v>16.346406549904</v>
       </c>
       <c r="E8">
-        <v>-8.1434</v>
+        <v>-7.932300000000001</v>
       </c>
       <c r="F8">
-        <v>1.2666</v>
+        <v>1.4777</v>
       </c>
       <c r="G8">
         <v>4.31</v>
@@ -1937,28 +1937,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M8">
-        <v>0.06370998</v>
+        <v>0.07432830999999998</v>
       </c>
       <c r="N8">
-        <v>1.719623353333333</v>
+        <v>1.709005023333333</v>
       </c>
       <c r="O8">
-        <v>0.2837378533</v>
+        <v>0.28198582885</v>
       </c>
       <c r="P8">
-        <v>1.435885500033333</v>
+        <v>1.427019194483333</v>
       </c>
       <c r="Q8">
-        <v>2.585885500033333</v>
+        <v>2.577019194483333</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1521764534017722</v>
+        <v>0.1531411038562227</v>
       </c>
       <c r="T8">
-        <v>2.073475075189136</v>
+        <v>2.092277908049322</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>27.99142823986655</v>
+        <v>23.99265277702848</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1453612615862871</v>
+        <v>0.1451566269749083</v>
       </c>
       <c r="C9">
-        <v>19.178706549904</v>
+        <v>19.00127355988235</v>
       </c>
       <c r="D9">
-        <v>16.346406549904</v>
+        <v>16.38007355988235</v>
       </c>
       <c r="E9">
-        <v>-7.9323</v>
+        <v>-7.7212</v>
       </c>
       <c r="F9">
-        <v>1.4777</v>
+        <v>1.6888</v>
       </c>
       <c r="G9">
         <v>4.31</v>
@@ -2019,28 +2019,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M9">
-        <v>0.07432830999999999</v>
+        <v>0.08494664</v>
       </c>
       <c r="N9">
-        <v>1.709005023333333</v>
+        <v>1.698386693333333</v>
       </c>
       <c r="O9">
-        <v>0.28198582885</v>
+        <v>0.2802338044</v>
       </c>
       <c r="P9">
-        <v>1.427019194483333</v>
+        <v>1.418152888933333</v>
       </c>
       <c r="Q9">
-        <v>2.577019194483333</v>
+        <v>2.568152888933334</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1531411038562227</v>
+        <v>0.1541267249727264</v>
       </c>
       <c r="T9">
-        <v>2.092277908049322</v>
+        <v>2.111489498145599</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>23.99265277702847</v>
+        <v>20.99357117989991</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1451566269749083</v>
+        <v>0.1449519923635295</v>
       </c>
       <c r="C10">
-        <v>19.00127355988235</v>
+        <v>18.82397953702291</v>
       </c>
       <c r="D10">
-        <v>16.38007355988235</v>
+        <v>16.41387953702291</v>
       </c>
       <c r="E10">
-        <v>-7.7212</v>
+        <v>-7.5101</v>
       </c>
       <c r="F10">
-        <v>1.6888</v>
+        <v>1.8999</v>
       </c>
       <c r="G10">
         <v>4.31</v>
@@ -2101,28 +2101,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M10">
-        <v>0.08494664</v>
+        <v>0.09556496999999999</v>
       </c>
       <c r="N10">
-        <v>1.698386693333333</v>
+        <v>1.687768363333333</v>
       </c>
       <c r="O10">
-        <v>0.2802338044</v>
+        <v>0.27848177995</v>
       </c>
       <c r="P10">
-        <v>1.418152888933333</v>
+        <v>1.409286583383333</v>
       </c>
       <c r="Q10">
-        <v>2.568152888933334</v>
+        <v>2.559286583383334</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1541267249727264</v>
+        <v>0.1551340080917907</v>
       </c>
       <c r="T10">
-        <v>2.111489498145599</v>
+        <v>2.131123320991245</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>20.99357117989991</v>
+        <v>18.66095215991104</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1449519923635295</v>
+        <v>0.1447473577521507</v>
       </c>
       <c r="C11">
-        <v>18.82397953702291</v>
+        <v>18.64682534352631</v>
       </c>
       <c r="D11">
-        <v>16.41387953702291</v>
+        <v>16.44782534352631</v>
       </c>
       <c r="E11">
-        <v>-7.5101</v>
+        <v>-7.299</v>
       </c>
       <c r="F11">
-        <v>1.8999</v>
+        <v>2.111</v>
       </c>
       <c r="G11">
         <v>4.31</v>
@@ -2183,28 +2183,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M11">
-        <v>0.09556496999999999</v>
+        <v>0.1061833</v>
       </c>
       <c r="N11">
-        <v>1.687768363333333</v>
+        <v>1.677150033333334</v>
       </c>
       <c r="O11">
-        <v>0.27848177995</v>
+        <v>0.2767297555000001</v>
       </c>
       <c r="P11">
-        <v>1.409286583383333</v>
+        <v>1.400420277833333</v>
       </c>
       <c r="Q11">
-        <v>2.559286583383334</v>
+        <v>2.550420277833334</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1551340080917907</v>
+        <v>0.1561636752801674</v>
       </c>
       <c r="T11">
-        <v>2.131123320991245</v>
+        <v>2.151193451011238</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>18.66095215991104</v>
+        <v>16.79485694391994</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1447473577521507</v>
+        <v>0.1445427231407719</v>
       </c>
       <c r="C12">
-        <v>18.64682534352631</v>
+        <v>18.46981184874047</v>
       </c>
       <c r="D12">
-        <v>16.44782534352631</v>
+        <v>16.48191184874047</v>
       </c>
       <c r="E12">
-        <v>-7.298999999999999</v>
+        <v>-7.0879</v>
       </c>
       <c r="F12">
-        <v>2.111</v>
+        <v>2.3221</v>
       </c>
       <c r="G12">
         <v>4.31</v>
@@ -2265,28 +2265,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M12">
-        <v>0.1061833</v>
+        <v>0.11680163</v>
       </c>
       <c r="N12">
-        <v>1.677150033333333</v>
+        <v>1.666531703333333</v>
       </c>
       <c r="O12">
-        <v>0.2767297555</v>
+        <v>0.27497773105</v>
       </c>
       <c r="P12">
-        <v>1.400420277833333</v>
+        <v>1.391553972283333</v>
       </c>
       <c r="Q12">
-        <v>2.550420277833333</v>
+        <v>2.541553972283333</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1561636752801674</v>
+        <v>0.1572164810570471</v>
       </c>
       <c r="T12">
-        <v>2.151193451011238</v>
+        <v>2.171714595188984</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>16.79485694391993</v>
+        <v>15.26805176719994</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1445427231407719</v>
+        <v>0.1443380885293931</v>
       </c>
       <c r="C13">
-        <v>18.46981184874047</v>
+        <v>18.29293992923486</v>
       </c>
       <c r="D13">
-        <v>16.48191184874047</v>
+        <v>16.51613992923486</v>
       </c>
       <c r="E13">
-        <v>-7.0879</v>
+        <v>-6.8768</v>
       </c>
       <c r="F13">
-        <v>2.3221</v>
+        <v>2.5332</v>
       </c>
       <c r="G13">
         <v>4.31</v>
@@ -2347,28 +2347,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M13">
-        <v>0.11680163</v>
+        <v>0.12741996</v>
       </c>
       <c r="N13">
-        <v>1.666531703333333</v>
+        <v>1.655913373333334</v>
       </c>
       <c r="O13">
-        <v>0.27497773105</v>
+        <v>0.2732257066000001</v>
       </c>
       <c r="P13">
-        <v>1.391553972283333</v>
+        <v>1.382687666733333</v>
       </c>
       <c r="Q13">
-        <v>2.541553972283333</v>
+        <v>2.532687666733334</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1572164810570471</v>
+        <v>0.1582932142379467</v>
       </c>
       <c r="T13">
-        <v>2.171714595188984</v>
+        <v>2.192702129007134</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.26805176719994</v>
+        <v>13.99571411993328</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1443380885293931</v>
+        <v>0.1441334539180143</v>
       </c>
       <c r="C14">
-        <v>18.29293992923486</v>
+        <v>18.11621046887557</v>
       </c>
       <c r="D14">
-        <v>16.51613992923486</v>
+        <v>16.55051046887557</v>
       </c>
       <c r="E14">
-        <v>-6.8768</v>
+        <v>-6.6657</v>
       </c>
       <c r="F14">
-        <v>2.5332</v>
+        <v>2.7443</v>
       </c>
       <c r="G14">
         <v>4.31</v>
@@ -2429,28 +2429,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M14">
-        <v>0.12741996</v>
+        <v>0.13803829</v>
       </c>
       <c r="N14">
-        <v>1.655913373333334</v>
+        <v>1.645295043333334</v>
       </c>
       <c r="O14">
-        <v>0.2732257066000001</v>
+        <v>0.2714736821500001</v>
       </c>
       <c r="P14">
-        <v>1.382687666733333</v>
+        <v>1.373821361183333</v>
       </c>
       <c r="Q14">
-        <v>2.532687666733334</v>
+        <v>2.523821361183334</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1582932142379467</v>
+        <v>0.1593946999057636</v>
       </c>
       <c r="T14">
-        <v>2.192702129007134</v>
+        <v>2.21417213486708</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>13.99571411993328</v>
+        <v>12.91912072609226</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1441334539180143</v>
+        <v>0.1441041693066355</v>
       </c>
       <c r="C15">
-        <v>18.11621046887557</v>
+        <v>17.91004083216148</v>
       </c>
       <c r="D15">
-        <v>16.55051046887557</v>
+        <v>16.55544083216148</v>
       </c>
       <c r="E15">
-        <v>-6.6657</v>
+        <v>-6.4546</v>
       </c>
       <c r="F15">
-        <v>2.7443</v>
+        <v>2.9554</v>
       </c>
       <c r="G15">
         <v>4.31</v>
@@ -2511,45 +2511,45 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M15">
-        <v>0.13803829</v>
+        <v>0.15308972</v>
       </c>
       <c r="N15">
-        <v>1.645295043333334</v>
+        <v>1.630243613333334</v>
       </c>
       <c r="O15">
-        <v>0.2714736821500001</v>
+        <v>0.2689901962</v>
       </c>
       <c r="P15">
-        <v>1.373821361183333</v>
+        <v>1.361253417133333</v>
       </c>
       <c r="Q15">
-        <v>2.523821361183334</v>
+        <v>2.511253417133334</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1593946999057636</v>
+        <v>0.1605218015193436</v>
       </c>
       <c r="T15">
-        <v>2.21417213486708</v>
+        <v>2.236141443188885</v>
       </c>
       <c r="U15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0.165</v>
       </c>
       <c r="W15">
-        <v>0.0420005</v>
+        <v>0.043253</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>12.91912072609226</v>
+        <v>11.64894241973487</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1441041693066355</v>
+        <v>0.1439120596952567</v>
       </c>
       <c r="C16">
-        <v>17.91004083216148</v>
+        <v>17.73135743124573</v>
       </c>
       <c r="D16">
-        <v>16.55544083216148</v>
+        <v>16.58785743124573</v>
       </c>
       <c r="E16">
-        <v>-6.4546</v>
+        <v>-6.243499999999999</v>
       </c>
       <c r="F16">
-        <v>2.9554</v>
+        <v>3.166500000000001</v>
       </c>
       <c r="G16">
         <v>4.31</v>
@@ -2593,28 +2593,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M16">
-        <v>0.15308972</v>
+        <v>0.1640247</v>
       </c>
       <c r="N16">
-        <v>1.630243613333334</v>
+        <v>1.619308633333334</v>
       </c>
       <c r="O16">
-        <v>0.2689901962</v>
+        <v>0.2671859245000001</v>
       </c>
       <c r="P16">
-        <v>1.361253417133333</v>
+        <v>1.352122708833333</v>
       </c>
       <c r="Q16">
-        <v>2.511253417133334</v>
+        <v>2.502122708833333</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1605218015193436</v>
+        <v>0.1616754231708903</v>
       </c>
       <c r="T16">
-        <v>2.236141443188885</v>
+        <v>2.25862767641238</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.64894241973487</v>
+        <v>10.87234625841921</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1439120596952567</v>
+        <v>0.1437199500838779</v>
       </c>
       <c r="C17">
-        <v>17.73135743124573</v>
+        <v>17.5528012268869</v>
       </c>
       <c r="D17">
-        <v>16.58785743124573</v>
+        <v>16.62040122688691</v>
       </c>
       <c r="E17">
-        <v>-6.243500000000001</v>
+        <v>-6.0324</v>
       </c>
       <c r="F17">
-        <v>3.1665</v>
+        <v>3.3776</v>
       </c>
       <c r="G17">
         <v>4.31</v>
@@ -2675,28 +2675,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M17">
-        <v>0.1640247</v>
+        <v>0.17495968</v>
       </c>
       <c r="N17">
-        <v>1.619308633333334</v>
+        <v>1.608373653333333</v>
       </c>
       <c r="O17">
-        <v>0.2671859245000001</v>
+        <v>0.2653816528</v>
       </c>
       <c r="P17">
-        <v>1.352122708833333</v>
+        <v>1.342992000533334</v>
       </c>
       <c r="Q17">
-        <v>2.502122708833333</v>
+        <v>2.492992000533333</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1616754231708903</v>
+        <v>0.1628565120046166</v>
       </c>
       <c r="T17">
-        <v>2.25862767641238</v>
+        <v>2.281649296141196</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.87234625841921</v>
+        <v>10.19282461726801</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1437199500838779</v>
+        <v>0.1437691554724991</v>
       </c>
       <c r="C18">
-        <v>17.5528012268869</v>
+        <v>17.33335356585558</v>
       </c>
       <c r="D18">
-        <v>16.62040122688691</v>
+        <v>16.61205356585558</v>
       </c>
       <c r="E18">
-        <v>-6.0324</v>
+        <v>-5.8213</v>
       </c>
       <c r="F18">
-        <v>3.3776</v>
+        <v>3.5887</v>
       </c>
       <c r="G18">
         <v>4.31</v>
@@ -2757,45 +2757,45 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M18">
-        <v>0.17495968</v>
+        <v>0.19199545</v>
       </c>
       <c r="N18">
-        <v>1.608373653333333</v>
+        <v>1.591337883333333</v>
       </c>
       <c r="O18">
-        <v>0.2653816528</v>
+        <v>0.26257075075</v>
       </c>
       <c r="P18">
-        <v>1.342992000533334</v>
+        <v>1.328767132583333</v>
       </c>
       <c r="Q18">
-        <v>2.492992000533333</v>
+        <v>2.478767132583333</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1628565120046166</v>
+        <v>0.1640660608102399</v>
       </c>
       <c r="T18">
-        <v>2.281649296141196</v>
+        <v>2.305225653694803</v>
       </c>
       <c r="U18">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V18">
         <v>0.165</v>
       </c>
       <c r="W18">
-        <v>0.043253</v>
+        <v>0.0446725</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>10.19282461726801</v>
+        <v>9.288414560518664</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1437691554724991</v>
+        <v>0.1435912408611203</v>
       </c>
       <c r="C19">
-        <v>17.33335356585558</v>
+        <v>17.15247638569453</v>
       </c>
       <c r="D19">
-        <v>16.61205356585558</v>
+        <v>16.64227638569453</v>
       </c>
       <c r="E19">
-        <v>-5.8213</v>
+        <v>-5.6102</v>
       </c>
       <c r="F19">
-        <v>3.5887</v>
+        <v>3.7998</v>
       </c>
       <c r="G19">
         <v>4.31</v>
@@ -2839,28 +2839,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M19">
-        <v>0.19199545</v>
+        <v>0.2032893</v>
       </c>
       <c r="N19">
-        <v>1.591337883333333</v>
+        <v>1.580044033333333</v>
       </c>
       <c r="O19">
-        <v>0.26257075075</v>
+        <v>0.2607072655</v>
       </c>
       <c r="P19">
-        <v>1.328767132583333</v>
+        <v>1.319336767833333</v>
       </c>
       <c r="Q19">
-        <v>2.478767132583333</v>
+        <v>2.469336767833334</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1640660608102399</v>
+        <v>0.1653051108062443</v>
       </c>
       <c r="T19">
-        <v>2.305225653694803</v>
+        <v>2.329377044359473</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>9.288414560518664</v>
+        <v>8.772391529378741</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1435912408611203</v>
+        <v>0.1434133262497415</v>
       </c>
       <c r="C20">
-        <v>17.15247638569453</v>
+        <v>16.97170937658191</v>
       </c>
       <c r="D20">
-        <v>16.64227638569453</v>
+        <v>16.67260937658191</v>
       </c>
       <c r="E20">
-        <v>-5.610200000000001</v>
+        <v>-5.3991</v>
       </c>
       <c r="F20">
-        <v>3.7998</v>
+        <v>4.0109</v>
       </c>
       <c r="G20">
         <v>4.31</v>
@@ -2921,28 +2921,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M20">
-        <v>0.2032893</v>
+        <v>0.21458315</v>
       </c>
       <c r="N20">
-        <v>1.580044033333333</v>
+        <v>1.568750183333333</v>
       </c>
       <c r="O20">
-        <v>0.2607072655</v>
+        <v>0.25884378025</v>
       </c>
       <c r="P20">
-        <v>1.319336767833333</v>
+        <v>1.309906403083333</v>
       </c>
       <c r="Q20">
-        <v>2.469336767833334</v>
+        <v>2.459906403083334</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1653051108062443</v>
+        <v>0.1665747546293105</v>
       </c>
       <c r="T20">
-        <v>2.329377044359473</v>
+        <v>2.354124765657839</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.772391529378741</v>
+        <v>8.310686712043015</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1434133262497415</v>
+        <v>0.1432354116383628</v>
       </c>
       <c r="C21">
-        <v>16.97170937658191</v>
+        <v>16.79105314202638</v>
       </c>
       <c r="D21">
-        <v>16.67260937658191</v>
+        <v>16.70305314202638</v>
       </c>
       <c r="E21">
-        <v>-5.3991</v>
+        <v>-5.188</v>
       </c>
       <c r="F21">
-        <v>4.0109</v>
+        <v>4.222</v>
       </c>
       <c r="G21">
         <v>4.31</v>
@@ -3003,28 +3003,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M21">
-        <v>0.21458315</v>
+        <v>0.225877</v>
       </c>
       <c r="N21">
-        <v>1.568750183333333</v>
+        <v>1.557456333333333</v>
       </c>
       <c r="O21">
-        <v>0.25884378025</v>
+        <v>0.256980295</v>
       </c>
       <c r="P21">
-        <v>1.309906403083333</v>
+        <v>1.300476038333333</v>
       </c>
       <c r="Q21">
-        <v>2.459906403083334</v>
+        <v>2.450476038333333</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1665747546293105</v>
+        <v>0.1678761395479534</v>
       </c>
       <c r="T21">
-        <v>2.354124765657839</v>
+        <v>2.379491179988664</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.310686712043015</v>
+        <v>7.895152376440865</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1432354116383628</v>
+        <v>0.1431977770269839</v>
       </c>
       <c r="C22">
-        <v>16.79105314202638</v>
+        <v>16.58640722068226</v>
       </c>
       <c r="D22">
-        <v>16.70305314202638</v>
+        <v>16.70950722068226</v>
       </c>
       <c r="E22">
-        <v>-5.188</v>
+        <v>-4.9769</v>
       </c>
       <c r="F22">
-        <v>4.222</v>
+        <v>4.4331</v>
       </c>
       <c r="G22">
         <v>4.31</v>
@@ -3085,45 +3085,45 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M22">
-        <v>0.225877</v>
+        <v>0.24071733</v>
       </c>
       <c r="N22">
-        <v>1.557456333333333</v>
+        <v>1.542616003333333</v>
       </c>
       <c r="O22">
-        <v>0.256980295</v>
+        <v>0.25453164055</v>
       </c>
       <c r="P22">
-        <v>1.300476038333333</v>
+        <v>1.288084362783333</v>
       </c>
       <c r="Q22">
-        <v>2.450476038333333</v>
+        <v>2.438084362783334</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1678761395479534</v>
+        <v>0.1692104709202328</v>
       </c>
       <c r="T22">
-        <v>2.379491179988664</v>
+        <v>2.405499782024067</v>
       </c>
       <c r="U22">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V22">
         <v>0.165</v>
       </c>
       <c r="W22">
-        <v>0.0446725</v>
+        <v>0.0453405</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y22">
-        <v>7.895152376440865</v>
+        <v>7.408412735939424</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1431977770269839</v>
+        <v>0.1430265424156051</v>
       </c>
       <c r="C23">
-        <v>16.58640722068226</v>
+        <v>16.40473587158537</v>
       </c>
       <c r="D23">
-        <v>16.70950722068226</v>
+        <v>16.73893587158537</v>
       </c>
       <c r="E23">
-        <v>-4.976900000000001</v>
+        <v>-4.7658</v>
       </c>
       <c r="F23">
-        <v>4.4331</v>
+        <v>4.6442</v>
       </c>
       <c r="G23">
         <v>4.31</v>
@@ -3167,28 +3167,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M23">
-        <v>0.24071733</v>
+        <v>0.25218006</v>
       </c>
       <c r="N23">
-        <v>1.542616003333333</v>
+        <v>1.531153273333334</v>
       </c>
       <c r="O23">
-        <v>0.25453164055</v>
+        <v>0.2526402901000001</v>
       </c>
       <c r="P23">
-        <v>1.288084362783333</v>
+        <v>1.278512983233334</v>
       </c>
       <c r="Q23">
-        <v>2.438084362783334</v>
+        <v>2.428512983233333</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1692104709202328</v>
+        <v>0.1705790159174425</v>
       </c>
       <c r="T23">
-        <v>2.405499782024067</v>
+        <v>2.432175271291147</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.408412735939425</v>
+        <v>7.071666702487634</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1430265424156051</v>
+        <v>0.1428553078042263</v>
       </c>
       <c r="C24">
-        <v>16.40473587158537</v>
+        <v>16.2231683643847</v>
       </c>
       <c r="D24">
-        <v>16.73893587158537</v>
+        <v>16.7684683643847</v>
       </c>
       <c r="E24">
-        <v>-4.7658</v>
+        <v>-4.5547</v>
       </c>
       <c r="F24">
-        <v>4.6442</v>
+        <v>4.8553</v>
       </c>
       <c r="G24">
         <v>4.31</v>
@@ -3249,28 +3249,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M24">
-        <v>0.25218006</v>
+        <v>0.26364279</v>
       </c>
       <c r="N24">
-        <v>1.531153273333334</v>
+        <v>1.519690543333333</v>
       </c>
       <c r="O24">
-        <v>0.2526402901000001</v>
+        <v>0.25074893965</v>
       </c>
       <c r="P24">
-        <v>1.278512983233334</v>
+        <v>1.268941603683333</v>
       </c>
       <c r="Q24">
-        <v>2.428512983233333</v>
+        <v>2.418941603683334</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1705790159174425</v>
+        <v>0.1719831075379563</v>
       </c>
       <c r="T24">
-        <v>2.432175271291147</v>
+        <v>2.459543630409319</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.071666702487634</v>
+        <v>6.764202932814257</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1428553078042263</v>
+        <v>0.1426840731928476</v>
       </c>
       <c r="C25">
-        <v>16.2231683643847</v>
+        <v>16.04170524967623</v>
       </c>
       <c r="D25">
-        <v>16.7684683643847</v>
+        <v>16.79810524967623</v>
       </c>
       <c r="E25">
-        <v>-4.5547</v>
+        <v>-4.343599999999999</v>
       </c>
       <c r="F25">
-        <v>4.8553</v>
+        <v>5.066400000000001</v>
       </c>
       <c r="G25">
         <v>4.31</v>
@@ -3331,28 +3331,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M25">
-        <v>0.26364279</v>
+        <v>0.27510552</v>
       </c>
       <c r="N25">
-        <v>1.519690543333333</v>
+        <v>1.508227813333333</v>
       </c>
       <c r="O25">
-        <v>0.25074893965</v>
+        <v>0.2488575892</v>
       </c>
       <c r="P25">
-        <v>1.268941603683333</v>
+        <v>1.259370224133333</v>
       </c>
       <c r="Q25">
-        <v>2.418941603683334</v>
+        <v>2.409370224133333</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1719831075379563</v>
+        <v>0.1734241489379573</v>
       </c>
       <c r="T25">
-        <v>2.459543630409319</v>
+        <v>2.487632209504286</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.764202932814257</v>
+        <v>6.482361143946996</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1426840731928476</v>
+        <v>0.1425128385814687</v>
       </c>
       <c r="C26">
-        <v>16.04170524967623</v>
+        <v>15.86034708195536</v>
       </c>
       <c r="D26">
-        <v>16.79810524967623</v>
+        <v>16.82784708195537</v>
       </c>
       <c r="E26">
-        <v>-4.3436</v>
+        <v>-4.1325</v>
       </c>
       <c r="F26">
-        <v>5.0664</v>
+        <v>5.2775</v>
       </c>
       <c r="G26">
         <v>4.31</v>
@@ -3413,28 +3413,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M26">
-        <v>0.27510552</v>
+        <v>0.28656825</v>
       </c>
       <c r="N26">
-        <v>1.508227813333333</v>
+        <v>1.496765083333333</v>
       </c>
       <c r="O26">
-        <v>0.2488575892</v>
+        <v>0.24696623875</v>
       </c>
       <c r="P26">
-        <v>1.259370224133333</v>
+        <v>1.249798844583333</v>
       </c>
       <c r="Q26">
-        <v>2.409370224133333</v>
+        <v>2.399798844583334</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1734241489379573</v>
+        <v>0.174903618108625</v>
       </c>
       <c r="T26">
-        <v>2.487632209504286</v>
+        <v>2.516469817375119</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.482361143946997</v>
+        <v>6.223066698189117</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1425128385814687</v>
+        <v>0.1425587039700899</v>
       </c>
       <c r="C27">
-        <v>15.86034708195536</v>
+        <v>15.64127037583588</v>
       </c>
       <c r="D27">
-        <v>16.82784708195537</v>
+        <v>16.81987037583588</v>
       </c>
       <c r="E27">
-        <v>-4.1325</v>
+        <v>-3.9214</v>
       </c>
       <c r="F27">
-        <v>5.2775</v>
+        <v>5.4886</v>
       </c>
       <c r="G27">
         <v>4.31</v>
@@ -3495,45 +3495,45 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M27">
-        <v>0.28656825</v>
+        <v>0.30351958</v>
       </c>
       <c r="N27">
-        <v>1.496765083333333</v>
+        <v>1.479813753333334</v>
       </c>
       <c r="O27">
-        <v>0.24696623875</v>
+        <v>0.2441692693</v>
       </c>
       <c r="P27">
-        <v>1.249798844583333</v>
+        <v>1.235644484033334</v>
       </c>
       <c r="Q27">
-        <v>2.399798844583334</v>
+        <v>2.385644484033334</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.174903618108625</v>
+        <v>0.176423072932554</v>
       </c>
       <c r="T27">
-        <v>2.516469817375119</v>
+        <v>2.546086820053271</v>
       </c>
       <c r="U27">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V27">
         <v>0.165</v>
       </c>
       <c r="W27">
-        <v>0.0453405</v>
+        <v>0.0461755</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y27">
-        <v>6.223066698189117</v>
+        <v>5.875513313946117</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1425587039700899</v>
+        <v>0.1423958193587112</v>
       </c>
       <c r="C28">
-        <v>15.64127037583588</v>
+        <v>15.45853286675731</v>
       </c>
       <c r="D28">
-        <v>16.81987037583588</v>
+        <v>16.84823286675731</v>
       </c>
       <c r="E28">
-        <v>-3.9214</v>
+        <v>-3.7103</v>
       </c>
       <c r="F28">
-        <v>5.4886</v>
+        <v>5.6997</v>
       </c>
       <c r="G28">
         <v>4.31</v>
@@ -3577,28 +3577,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M28">
-        <v>0.30351958</v>
+        <v>0.31519341</v>
       </c>
       <c r="N28">
-        <v>1.479813753333334</v>
+        <v>1.468139923333333</v>
       </c>
       <c r="O28">
-        <v>0.2441692693</v>
+        <v>0.24224308735</v>
       </c>
       <c r="P28">
-        <v>1.235644484033334</v>
+        <v>1.225896835983333</v>
       </c>
       <c r="Q28">
-        <v>2.385644484033334</v>
+        <v>2.375896835983333</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.176423072932554</v>
+        <v>0.1779841566557687</v>
       </c>
       <c r="T28">
-        <v>2.546086820053271</v>
+        <v>2.576515247462333</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.875513313946117</v>
+        <v>5.657901709725889</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1423958193587112</v>
+        <v>0.1422329347473323</v>
       </c>
       <c r="C29">
-        <v>15.45853286675731</v>
+        <v>15.2758911716934</v>
       </c>
       <c r="D29">
-        <v>16.84823286675731</v>
+        <v>16.8766911716934</v>
       </c>
       <c r="E29">
-        <v>-3.7103</v>
+        <v>-3.4992</v>
       </c>
       <c r="F29">
-        <v>5.6997</v>
+        <v>5.9108</v>
       </c>
       <c r="G29">
         <v>4.31</v>
@@ -3659,28 +3659,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M29">
-        <v>0.31519341</v>
+        <v>0.32686724</v>
       </c>
       <c r="N29">
-        <v>1.468139923333333</v>
+        <v>1.456466093333333</v>
       </c>
       <c r="O29">
-        <v>0.24224308735</v>
+        <v>0.2403169054</v>
       </c>
       <c r="P29">
-        <v>1.225896835983333</v>
+        <v>1.216149187933333</v>
       </c>
       <c r="Q29">
-        <v>2.375896835983333</v>
+        <v>2.366149187933333</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1779841566557687</v>
+        <v>0.1795886038157394</v>
       </c>
       <c r="T29">
-        <v>2.576515247462333</v>
+        <v>2.60778890896609</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.657901709725889</v>
+        <v>5.455833791521393</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1422329347473323</v>
+        <v>0.1420700501359536</v>
       </c>
       <c r="C30">
-        <v>15.2758911716934</v>
+        <v>15.09334577698319</v>
       </c>
       <c r="D30">
-        <v>16.8766911716934</v>
+        <v>16.90524577698319</v>
       </c>
       <c r="E30">
-        <v>-3.4992</v>
+        <v>-3.288099999999999</v>
       </c>
       <c r="F30">
-        <v>5.9108</v>
+        <v>6.121900000000001</v>
       </c>
       <c r="G30">
         <v>4.31</v>
@@ -3741,28 +3741,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M30">
-        <v>0.32686724</v>
+        <v>0.3385410700000001</v>
       </c>
       <c r="N30">
-        <v>1.456466093333333</v>
+        <v>1.444792263333333</v>
       </c>
       <c r="O30">
-        <v>0.2403169054</v>
+        <v>0.23839072345</v>
       </c>
       <c r="P30">
-        <v>1.216149187933333</v>
+        <v>1.206401539883333</v>
       </c>
       <c r="Q30">
-        <v>2.366149187933333</v>
+        <v>2.356401539883334</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1795886038157394</v>
+        <v>0.1812382466703571</v>
       </c>
       <c r="T30">
-        <v>2.60778890896609</v>
+        <v>2.63994351868122</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.455833791521393</v>
+        <v>5.267701591813759</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1420700501359535</v>
+        <v>0.1419071655245747</v>
       </c>
       <c r="C31">
-        <v>15.0933457769832</v>
+        <v>14.9108971722628</v>
       </c>
       <c r="D31">
-        <v>16.9052457769832</v>
+        <v>16.9338971722628</v>
       </c>
       <c r="E31">
-        <v>-3.288100000000001</v>
+        <v>-3.077000000000001</v>
       </c>
       <c r="F31">
-        <v>6.121899999999999</v>
+        <v>6.332999999999999</v>
       </c>
       <c r="G31">
         <v>4.31</v>
@@ -3823,28 +3823,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M31">
-        <v>0.3385410699999999</v>
+        <v>0.3502149</v>
       </c>
       <c r="N31">
-        <v>1.444792263333333</v>
+        <v>1.433118433333334</v>
       </c>
       <c r="O31">
-        <v>0.23839072345</v>
+        <v>0.2364645415</v>
       </c>
       <c r="P31">
-        <v>1.206401539883333</v>
+        <v>1.196653891833334</v>
       </c>
       <c r="Q31">
-        <v>2.356401539883334</v>
+        <v>2.346653891833334</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1812382466703571</v>
+        <v>0.1829350221779639</v>
       </c>
       <c r="T31">
-        <v>2.63994351868122</v>
+        <v>2.673016831531068</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.26770159181376</v>
+        <v>5.092111538753302</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1419071655245747</v>
+        <v>0.1417442809131959</v>
       </c>
       <c r="C32">
-        <v>14.9108971722628</v>
+        <v>14.72854585049333</v>
       </c>
       <c r="D32">
-        <v>16.9338971722628</v>
+        <v>16.96264585049333</v>
       </c>
       <c r="E32">
-        <v>-3.077000000000001</v>
+        <v>-2.865900000000001</v>
       </c>
       <c r="F32">
-        <v>6.332999999999999</v>
+        <v>6.544099999999999</v>
       </c>
       <c r="G32">
         <v>4.31</v>
@@ -3905,28 +3905,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M32">
-        <v>0.3502149</v>
+        <v>0.36188873</v>
       </c>
       <c r="N32">
-        <v>1.433118433333334</v>
+        <v>1.421444603333333</v>
       </c>
       <c r="O32">
-        <v>0.2364645415</v>
+        <v>0.23453835955</v>
       </c>
       <c r="P32">
-        <v>1.196653891833334</v>
+        <v>1.186906243783334</v>
       </c>
       <c r="Q32">
-        <v>2.346653891833334</v>
+        <v>2.336906243783334</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1829350221779639</v>
+        <v>0.184680979584342</v>
       </c>
       <c r="T32">
-        <v>2.673016831531068</v>
+        <v>2.707048791130187</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.092111538753302</v>
+        <v>4.927849876212872</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1417442809131959</v>
+        <v>0.1415813963018172</v>
       </c>
       <c r="C33">
-        <v>14.72854585049333</v>
+        <v>14.54629230798917</v>
       </c>
       <c r="D33">
-        <v>16.96264585049333</v>
+        <v>16.99149230798918</v>
       </c>
       <c r="E33">
-        <v>-2.865900000000001</v>
+        <v>-2.6548</v>
       </c>
       <c r="F33">
-        <v>6.544099999999999</v>
+        <v>6.7552</v>
       </c>
       <c r="G33">
         <v>4.31</v>
@@ -3987,28 +3987,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M33">
-        <v>0.36188873</v>
+        <v>0.37356256</v>
       </c>
       <c r="N33">
-        <v>1.421444603333333</v>
+        <v>1.409770773333333</v>
       </c>
       <c r="O33">
-        <v>0.23453835955</v>
+        <v>0.2326121776</v>
       </c>
       <c r="P33">
-        <v>1.186906243783334</v>
+        <v>1.177158595733333</v>
       </c>
       <c r="Q33">
-        <v>2.336906243783334</v>
+        <v>2.327158595733334</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.184680979584342</v>
+        <v>0.1864782886791429</v>
       </c>
       <c r="T33">
-        <v>2.707048791130187</v>
+        <v>2.742081690717516</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.927849876212872</v>
+        <v>4.773854567581219</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1415813963018172</v>
+        <v>0.1414185116904383</v>
       </c>
       <c r="C34">
-        <v>14.54629230798917</v>
+        <v>14.36413704444663</v>
       </c>
       <c r="D34">
-        <v>16.99149230798918</v>
+        <v>17.02043704444663</v>
       </c>
       <c r="E34">
-        <v>-2.6548</v>
+        <v>-2.4437</v>
       </c>
       <c r="F34">
-        <v>6.7552</v>
+        <v>6.9663</v>
       </c>
       <c r="G34">
         <v>4.31</v>
@@ -4069,28 +4069,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M34">
-        <v>0.37356256</v>
+        <v>0.38523639</v>
       </c>
       <c r="N34">
-        <v>1.409770773333333</v>
+        <v>1.398096943333333</v>
       </c>
       <c r="O34">
-        <v>0.2326121776</v>
+        <v>0.23068599565</v>
       </c>
       <c r="P34">
-        <v>1.177158595733333</v>
+        <v>1.167410947683333</v>
       </c>
       <c r="Q34">
-        <v>2.327158595733334</v>
+        <v>2.317410947683333</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1864782886791429</v>
+        <v>0.188329248791699</v>
       </c>
       <c r="T34">
-        <v>2.742081690717516</v>
+        <v>2.778160348501482</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.773854567581219</v>
+        <v>4.629192307957545</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1414185116904383</v>
+        <v>0.1419653770790595</v>
       </c>
       <c r="C35">
-        <v>14.36413704444663</v>
+        <v>14.05624661735599</v>
       </c>
       <c r="D35">
-        <v>17.02043704444663</v>
+        <v>16.92364661735599</v>
       </c>
       <c r="E35">
-        <v>-2.4437</v>
+        <v>-2.2326</v>
       </c>
       <c r="F35">
-        <v>6.9663</v>
+        <v>7.1774</v>
       </c>
       <c r="G35">
         <v>4.31</v>
@@ -4151,45 +4151,45 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M35">
-        <v>0.38523639</v>
+        <v>0.41485372</v>
       </c>
       <c r="N35">
-        <v>1.398096943333333</v>
+        <v>1.368479613333333</v>
       </c>
       <c r="O35">
-        <v>0.23068599565</v>
+        <v>0.2257991362</v>
       </c>
       <c r="P35">
-        <v>1.167410947683333</v>
+        <v>1.142680477133333</v>
       </c>
       <c r="Q35">
-        <v>2.317410947683333</v>
+        <v>2.292680477133334</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.188329248791699</v>
+        <v>0.1902362986046357</v>
       </c>
       <c r="T35">
-        <v>2.778160348501482</v>
+        <v>2.815332298945567</v>
       </c>
       <c r="U35">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V35">
         <v>0.165</v>
       </c>
       <c r="W35">
-        <v>0.0461755</v>
+        <v>0.048263</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y35">
-        <v>4.629192307957545</v>
+        <v>4.298703970482254</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1419653770790595</v>
+        <v>0.1418233674676807</v>
       </c>
       <c r="C36">
-        <v>14.05624661735599</v>
+        <v>13.87017511346712</v>
       </c>
       <c r="D36">
-        <v>16.92364661735599</v>
+        <v>16.94867511346712</v>
       </c>
       <c r="E36">
-        <v>-2.2326</v>
+        <v>-2.0215</v>
       </c>
       <c r="F36">
-        <v>7.1774</v>
+        <v>7.388500000000001</v>
       </c>
       <c r="G36">
         <v>4.31</v>
@@ -4233,28 +4233,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M36">
-        <v>0.41485372</v>
+        <v>0.4270553000000001</v>
       </c>
       <c r="N36">
-        <v>1.368479613333333</v>
+        <v>1.356278033333333</v>
       </c>
       <c r="O36">
-        <v>0.2257991362</v>
+        <v>0.2237858755</v>
       </c>
       <c r="P36">
-        <v>1.142680477133333</v>
+        <v>1.132492157833333</v>
       </c>
       <c r="Q36">
-        <v>2.292680477133334</v>
+        <v>2.282492157833333</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1902362986046357</v>
+        <v>0.192202026873355</v>
       </c>
       <c r="T36">
-        <v>2.815332298945567</v>
+        <v>2.853648001711009</v>
       </c>
       <c r="U36">
         <v>0.0578</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.298703970482254</v>
+        <v>4.175883857039903</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1418233674676807</v>
+        <v>0.1416813578563019</v>
       </c>
       <c r="C37">
-        <v>13.87017511346712</v>
+        <v>13.68417774884966</v>
       </c>
       <c r="D37">
-        <v>16.94867511346712</v>
+        <v>16.97377774884966</v>
       </c>
       <c r="E37">
-        <v>-2.0215</v>
+        <v>-1.8104</v>
       </c>
       <c r="F37">
-        <v>7.388500000000001</v>
+        <v>7.599600000000001</v>
       </c>
       <c r="G37">
         <v>4.31</v>
@@ -4315,28 +4315,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M37">
-        <v>0.4270553000000001</v>
+        <v>0.4392568800000001</v>
       </c>
       <c r="N37">
-        <v>1.356278033333333</v>
+        <v>1.344076453333333</v>
       </c>
       <c r="O37">
-        <v>0.2237858755</v>
+        <v>0.2217726148</v>
       </c>
       <c r="P37">
-        <v>1.132492157833333</v>
+        <v>1.122303838533333</v>
       </c>
       <c r="Q37">
-        <v>2.282492157833333</v>
+        <v>2.272303838533333</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.192202026873355</v>
+        <v>0.1942291841504718</v>
       </c>
       <c r="T37">
-        <v>2.853648001711009</v>
+        <v>2.893161070187871</v>
       </c>
       <c r="U37">
         <v>0.0578</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.175883857039903</v>
+        <v>4.05988708323324</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.141681357856302</v>
+        <v>0.1426206732449231</v>
       </c>
       <c r="C38">
-        <v>13.68417774884965</v>
+        <v>13.30840495627158</v>
       </c>
       <c r="D38">
-        <v>16.97377774884965</v>
+        <v>16.80910495627159</v>
       </c>
       <c r="E38">
-        <v>-1.8104</v>
+        <v>-1.5993</v>
       </c>
       <c r="F38">
-        <v>7.5996</v>
+        <v>7.8107</v>
       </c>
       <c r="G38">
         <v>4.31</v>
@@ -4397,45 +4397,45 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M38">
-        <v>0.43925688</v>
+        <v>0.47879591</v>
       </c>
       <c r="N38">
-        <v>1.344076453333333</v>
+        <v>1.304537423333334</v>
       </c>
       <c r="O38">
-        <v>0.2217726148</v>
+        <v>0.21524867485</v>
       </c>
       <c r="P38">
-        <v>1.122303838533333</v>
+        <v>1.089288748483334</v>
       </c>
       <c r="Q38">
-        <v>2.272303838533333</v>
+        <v>2.239288748483334</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1942291841504718</v>
+        <v>0.1963206956268621</v>
       </c>
       <c r="T38">
-        <v>2.893161070187871</v>
+        <v>2.933928521790983</v>
       </c>
       <c r="U38">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V38">
         <v>0.165</v>
       </c>
       <c r="W38">
-        <v>0.048263</v>
+        <v>0.05118549999999999</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y38">
-        <v>4.059887083233241</v>
+        <v>3.724621067321426</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1426206732449231</v>
+        <v>0.1425078886335444</v>
       </c>
       <c r="C39">
-        <v>13.30840495627158</v>
+        <v>13.11690840741611</v>
       </c>
       <c r="D39">
-        <v>16.80910495627159</v>
+        <v>16.82870840741611</v>
       </c>
       <c r="E39">
-        <v>-1.5993</v>
+        <v>-1.388199999999999</v>
       </c>
       <c r="F39">
-        <v>7.8107</v>
+        <v>8.021800000000001</v>
       </c>
       <c r="G39">
         <v>4.31</v>
@@ -4479,28 +4479,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M39">
-        <v>0.47879591</v>
+        <v>0.49173634</v>
       </c>
       <c r="N39">
-        <v>1.304537423333334</v>
+        <v>1.291596993333333</v>
       </c>
       <c r="O39">
-        <v>0.21524867485</v>
+        <v>0.2131135039</v>
       </c>
       <c r="P39">
-        <v>1.089288748483334</v>
+        <v>1.078483489433333</v>
       </c>
       <c r="Q39">
-        <v>2.239288748483334</v>
+        <v>2.228483489433334</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1963206956268621</v>
+        <v>0.1984796752153941</v>
       </c>
       <c r="T39">
-        <v>2.933928521790983</v>
+        <v>2.976011052478066</v>
       </c>
       <c r="U39">
         <v>0.0613</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.724621067321426</v>
+        <v>3.626604723444546</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1425078886335444</v>
+        <v>0.1423951040221655</v>
       </c>
       <c r="C40">
-        <v>13.11690840741611</v>
+        <v>12.92545763660792</v>
       </c>
       <c r="D40">
-        <v>16.82870840741611</v>
+        <v>16.84835763660792</v>
       </c>
       <c r="E40">
-        <v>-1.388199999999999</v>
+        <v>-1.177099999999999</v>
       </c>
       <c r="F40">
-        <v>8.021800000000001</v>
+        <v>8.232900000000001</v>
       </c>
       <c r="G40">
         <v>4.31</v>
@@ -4561,28 +4561,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M40">
-        <v>0.49173634</v>
+        <v>0.50467677</v>
       </c>
       <c r="N40">
-        <v>1.291596993333333</v>
+        <v>1.278656563333334</v>
       </c>
       <c r="O40">
-        <v>0.2131135039</v>
+        <v>0.21097833295</v>
       </c>
       <c r="P40">
-        <v>1.078483489433333</v>
+        <v>1.067678230383333</v>
       </c>
       <c r="Q40">
-        <v>2.228483489433334</v>
+        <v>2.217678230383334</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1984796752153941</v>
+        <v>0.2007094410199435</v>
       </c>
       <c r="T40">
-        <v>2.976011052478066</v>
+        <v>3.019473338269643</v>
       </c>
       <c r="U40">
         <v>0.0613</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.626604723444546</v>
+        <v>3.53361485874084</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1423951040221655</v>
+        <v>0.1432175194107868</v>
       </c>
       <c r="C41">
-        <v>12.92545763660792</v>
+        <v>12.57212091494689</v>
       </c>
       <c r="D41">
-        <v>16.84835763660792</v>
+        <v>16.70612091494689</v>
       </c>
       <c r="E41">
-        <v>-1.177099999999999</v>
+        <v>-0.9659999999999993</v>
       </c>
       <c r="F41">
-        <v>8.232900000000001</v>
+        <v>8.444000000000001</v>
       </c>
       <c r="G41">
         <v>4.31</v>
@@ -4643,45 +4643,45 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M41">
-        <v>0.50467677</v>
+        <v>0.5412604000000001</v>
       </c>
       <c r="N41">
-        <v>1.278656563333334</v>
+        <v>1.242072933333333</v>
       </c>
       <c r="O41">
-        <v>0.21097833295</v>
+        <v>0.204942034</v>
       </c>
       <c r="P41">
-        <v>1.067678230383333</v>
+        <v>1.037130899333333</v>
       </c>
       <c r="Q41">
-        <v>2.217678230383334</v>
+        <v>2.187130899333333</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2007094410199435</v>
+        <v>0.2030135323513113</v>
       </c>
       <c r="T41">
-        <v>3.019473338269643</v>
+        <v>3.06438436692094</v>
       </c>
       <c r="U41">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V41">
         <v>0.165</v>
       </c>
       <c r="W41">
-        <v>0.05118549999999999</v>
+        <v>0.0535235</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>3.53361485874084</v>
+        <v>3.294778877843886</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1432175194107868</v>
+        <v>0.143128114799408</v>
       </c>
       <c r="C42">
-        <v>12.57212091494689</v>
+        <v>12.37636698685145</v>
       </c>
       <c r="D42">
-        <v>16.70612091494689</v>
+        <v>16.72146698685146</v>
       </c>
       <c r="E42">
-        <v>-0.9659999999999993</v>
+        <v>-0.7548999999999992</v>
       </c>
       <c r="F42">
-        <v>8.444000000000001</v>
+        <v>8.655100000000001</v>
       </c>
       <c r="G42">
         <v>4.31</v>
@@ -4725,28 +4725,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M42">
-        <v>0.5412604000000001</v>
+        <v>0.5547919100000001</v>
       </c>
       <c r="N42">
-        <v>1.242072933333333</v>
+        <v>1.228541423333333</v>
       </c>
       <c r="O42">
-        <v>0.204942034</v>
+        <v>0.20270933485</v>
       </c>
       <c r="P42">
-        <v>1.037130899333333</v>
+        <v>1.025832088483333</v>
       </c>
       <c r="Q42">
-        <v>2.187130899333333</v>
+        <v>2.175832088483333</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2030135323513113</v>
+        <v>0.2053957284735728</v>
       </c>
       <c r="T42">
-        <v>3.06438436692094</v>
+        <v>3.110817803323129</v>
       </c>
       <c r="U42">
         <v>0.0641</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.294778877843886</v>
+        <v>3.21441841740867</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.143128114799408</v>
+        <v>0.1430387101880292</v>
       </c>
       <c r="C43">
-        <v>12.37636698685145</v>
+        <v>12.18064127816766</v>
       </c>
       <c r="D43">
-        <v>16.72146698685146</v>
+        <v>16.73684127816767</v>
       </c>
       <c r="E43">
-        <v>-0.7548999999999992</v>
+        <v>-0.5437999999999992</v>
       </c>
       <c r="F43">
-        <v>8.655100000000001</v>
+        <v>8.866200000000001</v>
       </c>
       <c r="G43">
         <v>4.31</v>
@@ -4807,28 +4807,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M43">
-        <v>0.5547919100000001</v>
+        <v>0.5683234200000001</v>
       </c>
       <c r="N43">
-        <v>1.228541423333333</v>
+        <v>1.215009913333333</v>
       </c>
       <c r="O43">
-        <v>0.20270933485</v>
+        <v>0.2004766357</v>
       </c>
       <c r="P43">
-        <v>1.025832088483333</v>
+        <v>1.014533277633333</v>
       </c>
       <c r="Q43">
-        <v>2.175832088483333</v>
+        <v>2.164533277633333</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2053957284735728</v>
+        <v>0.2078600692897055</v>
       </c>
       <c r="T43">
-        <v>3.110817803323129</v>
+        <v>3.158852392704703</v>
       </c>
       <c r="U43">
         <v>0.0641</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.21441841740867</v>
+        <v>3.137884645565606</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1430387101880292</v>
+        <v>0.1429493055766504</v>
       </c>
       <c r="C44">
-        <v>12.18064127816767</v>
+        <v>11.98494386680482</v>
       </c>
       <c r="D44">
-        <v>16.73684127816767</v>
+        <v>16.75224386680483</v>
       </c>
       <c r="E44">
-        <v>-0.5438000000000009</v>
+        <v>-0.3327000000000009</v>
       </c>
       <c r="F44">
-        <v>8.866199999999999</v>
+        <v>9.077299999999999</v>
       </c>
       <c r="G44">
         <v>4.31</v>
@@ -4889,28 +4889,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M44">
-        <v>0.56832342</v>
+        <v>0.58185493</v>
       </c>
       <c r="N44">
-        <v>1.215009913333333</v>
+        <v>1.201478403333333</v>
       </c>
       <c r="O44">
-        <v>0.2004766357</v>
+        <v>0.19824393655</v>
       </c>
       <c r="P44">
-        <v>1.014533277633333</v>
+        <v>1.003234466783334</v>
       </c>
       <c r="Q44">
-        <v>2.164533277633334</v>
+        <v>2.153234466783334</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2078600692897054</v>
+        <v>0.2104108782046497</v>
       </c>
       <c r="T44">
-        <v>3.158852392704703</v>
+        <v>3.208572406275104</v>
       </c>
       <c r="U44">
         <v>0.0641</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.137884645565606</v>
+        <v>3.064910584040825</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1429493055766504</v>
+        <v>0.1457256209652716</v>
       </c>
       <c r="C45">
-        <v>11.98494386680482</v>
+        <v>11.30840255163393</v>
       </c>
       <c r="D45">
-        <v>16.75224386680483</v>
+        <v>16.28680255163393</v>
       </c>
       <c r="E45">
-        <v>-0.3327000000000009</v>
+        <v>-0.1216000000000008</v>
       </c>
       <c r="F45">
-        <v>9.077299999999999</v>
+        <v>9.288399999999999</v>
       </c>
       <c r="G45">
         <v>4.31</v>
@@ -4971,45 +4971,45 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M45">
-        <v>0.58185493</v>
+        <v>0.66783596</v>
       </c>
       <c r="N45">
-        <v>1.201478403333333</v>
+        <v>1.115497373333334</v>
       </c>
       <c r="O45">
-        <v>0.19824393655</v>
+        <v>0.1840570666</v>
       </c>
       <c r="P45">
-        <v>1.003234466783334</v>
+        <v>0.9314403067333334</v>
       </c>
       <c r="Q45">
-        <v>2.153234466783334</v>
+        <v>2.081440306733334</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2104108782046497</v>
+        <v>0.2130527874379849</v>
       </c>
       <c r="T45">
-        <v>3.208572406275104</v>
+        <v>3.260068134615876</v>
       </c>
       <c r="U45">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V45">
         <v>0.165</v>
       </c>
       <c r="W45">
-        <v>0.0535235</v>
+        <v>0.0600365</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>3.064910584040825</v>
+        <v>2.670316425209169</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1457256209652716</v>
+        <v>0.1457013463538928</v>
       </c>
       <c r="C46">
-        <v>11.30840255163393</v>
+        <v>11.10126001384012</v>
       </c>
       <c r="D46">
-        <v>16.28680255163393</v>
+        <v>16.29076001384012</v>
       </c>
       <c r="E46">
-        <v>-0.1216000000000008</v>
+        <v>0.08949999999999925</v>
       </c>
       <c r="F46">
-        <v>9.288399999999999</v>
+        <v>9.499499999999999</v>
       </c>
       <c r="G46">
         <v>4.31</v>
@@ -5053,28 +5053,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M46">
-        <v>0.66783596</v>
+        <v>0.68301405</v>
       </c>
       <c r="N46">
-        <v>1.115497373333334</v>
+        <v>1.100319283333334</v>
       </c>
       <c r="O46">
-        <v>0.1840570666</v>
+        <v>0.18155268175</v>
       </c>
       <c r="P46">
-        <v>0.9314403067333334</v>
+        <v>0.9187666015833335</v>
       </c>
       <c r="Q46">
-        <v>2.081440306733334</v>
+        <v>2.068766601583333</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2130527874379849</v>
+        <v>0.2157907660979868</v>
       </c>
       <c r="T46">
-        <v>3.260068134615876</v>
+        <v>3.313436434896313</v>
       </c>
       <c r="U46">
         <v>0.07190000000000001</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.670316425209169</v>
+        <v>2.61097606020452</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1457013463538928</v>
+        <v>0.145677071742514</v>
       </c>
       <c r="C47">
-        <v>11.10126001384012</v>
+        <v>10.89411939972822</v>
       </c>
       <c r="D47">
-        <v>16.29076001384012</v>
+        <v>16.29471939972822</v>
       </c>
       <c r="E47">
-        <v>0.08949999999999925</v>
+        <v>0.3005999999999993</v>
       </c>
       <c r="F47">
-        <v>9.499499999999999</v>
+        <v>9.710599999999999</v>
       </c>
       <c r="G47">
         <v>4.31</v>
@@ -5135,28 +5135,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M47">
-        <v>0.68301405</v>
+        <v>0.69819214</v>
       </c>
       <c r="N47">
-        <v>1.100319283333334</v>
+        <v>1.085141193333333</v>
       </c>
       <c r="O47">
-        <v>0.18155268175</v>
+        <v>0.1790482969</v>
       </c>
       <c r="P47">
-        <v>0.9187666015833335</v>
+        <v>0.9060928964333335</v>
       </c>
       <c r="Q47">
-        <v>2.068766601583333</v>
+        <v>2.056092896433333</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2157907660979868</v>
+        <v>0.2186301513750258</v>
       </c>
       <c r="T47">
-        <v>3.313436434896313</v>
+        <v>3.368781338890841</v>
       </c>
       <c r="U47">
         <v>0.07190000000000001</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.61097606020452</v>
+        <v>2.55421571106964</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.145677071742514</v>
+        <v>0.1471833521311352</v>
       </c>
       <c r="C48">
-        <v>10.89411939972822</v>
+        <v>10.44092426523168</v>
       </c>
       <c r="D48">
-        <v>16.29471939972822</v>
+        <v>16.05262426523169</v>
       </c>
       <c r="E48">
-        <v>0.3005999999999993</v>
+        <v>0.5116999999999994</v>
       </c>
       <c r="F48">
-        <v>9.710599999999999</v>
+        <v>9.9217</v>
       </c>
       <c r="G48">
         <v>4.31</v>
@@ -5217,45 +5217,45 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M48">
-        <v>0.69819214</v>
+        <v>0.7520648600000001</v>
       </c>
       <c r="N48">
-        <v>1.085141193333333</v>
+        <v>1.031268473333333</v>
       </c>
       <c r="O48">
-        <v>0.1790482969</v>
+        <v>0.1701592981</v>
       </c>
       <c r="P48">
-        <v>0.9060928964333335</v>
+        <v>0.8611091752333333</v>
       </c>
       <c r="Q48">
-        <v>2.056092896433333</v>
+        <v>2.011109175233333</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2186301513750258</v>
+        <v>0.2215766832662928</v>
       </c>
       <c r="T48">
-        <v>3.368781338890841</v>
+        <v>3.426214729828558</v>
       </c>
       <c r="U48">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V48">
         <v>0.165</v>
       </c>
       <c r="W48">
-        <v>0.0600365</v>
+        <v>0.063293</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.55421571106964</v>
+        <v>2.371249380450156</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1471833521311352</v>
+        <v>0.1471916425197564</v>
       </c>
       <c r="C49">
-        <v>10.44092426523168</v>
+        <v>10.22851170642268</v>
       </c>
       <c r="D49">
-        <v>16.05262426523169</v>
+        <v>16.05131170642268</v>
       </c>
       <c r="E49">
-        <v>0.5116999999999994</v>
+        <v>0.7228000000000012</v>
       </c>
       <c r="F49">
-        <v>9.9217</v>
+        <v>10.1328</v>
       </c>
       <c r="G49">
         <v>4.31</v>
@@ -5299,28 +5299,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M49">
-        <v>0.7520648600000001</v>
+        <v>0.7680662400000001</v>
       </c>
       <c r="N49">
-        <v>1.031268473333333</v>
+        <v>1.015267093333333</v>
       </c>
       <c r="O49">
-        <v>0.1701592981</v>
+        <v>0.1675190704</v>
       </c>
       <c r="P49">
-        <v>0.8611091752333333</v>
+        <v>0.8477480229333332</v>
       </c>
       <c r="Q49">
-        <v>2.011109175233333</v>
+        <v>1.997748022933333</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2215766832662928</v>
+        <v>0.2246365433072238</v>
       </c>
       <c r="T49">
-        <v>3.426214729828558</v>
+        <v>3.485857097340803</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.371249380450156</v>
+        <v>2.321848351690777</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1471916425197564</v>
+        <v>0.1471999329083776</v>
       </c>
       <c r="C50">
-        <v>10.22851170642268</v>
+        <v>10.01609936224148</v>
       </c>
       <c r="D50">
-        <v>16.05131170642268</v>
+        <v>16.04999936224148</v>
       </c>
       <c r="E50">
-        <v>0.7227999999999994</v>
+        <v>0.9338999999999995</v>
       </c>
       <c r="F50">
-        <v>10.1328</v>
+        <v>10.3439</v>
       </c>
       <c r="G50">
         <v>4.31</v>
@@ -5381,28 +5381,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M50">
-        <v>0.76806624</v>
+        <v>0.7840676200000001</v>
       </c>
       <c r="N50">
-        <v>1.015267093333333</v>
+        <v>0.9992657133333334</v>
       </c>
       <c r="O50">
-        <v>0.1675190704</v>
+        <v>0.1648788427</v>
       </c>
       <c r="P50">
-        <v>0.8477480229333334</v>
+        <v>0.8343868706333334</v>
       </c>
       <c r="Q50">
-        <v>1.997748022933334</v>
+        <v>1.984386870633334</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2246365433072238</v>
+        <v>0.2278163978595639</v>
       </c>
       <c r="T50">
-        <v>3.485857097340803</v>
+        <v>3.547838381226077</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.321848351690778</v>
+        <v>2.274463691452191</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1471999329083776</v>
+        <v>0.1472082232969988</v>
       </c>
       <c r="C51">
-        <v>10.01609936224148</v>
+        <v>9.803687232635454</v>
       </c>
       <c r="D51">
-        <v>16.04999936224148</v>
+        <v>16.04868723263546</v>
       </c>
       <c r="E51">
-        <v>0.9338999999999995</v>
+        <v>1.145</v>
       </c>
       <c r="F51">
-        <v>10.3439</v>
+        <v>10.555</v>
       </c>
       <c r="G51">
         <v>4.31</v>
@@ -5463,28 +5463,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M51">
-        <v>0.7840676200000001</v>
+        <v>0.800069</v>
       </c>
       <c r="N51">
-        <v>0.9992657133333334</v>
+        <v>0.9832643333333334</v>
       </c>
       <c r="O51">
-        <v>0.1648788427</v>
+        <v>0.162238615</v>
       </c>
       <c r="P51">
-        <v>0.8343868706333334</v>
+        <v>0.8210257183333334</v>
       </c>
       <c r="Q51">
-        <v>1.984386870633334</v>
+        <v>1.971025718333334</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2278163978595639</v>
+        <v>0.2311234465939975</v>
       </c>
       <c r="T51">
-        <v>3.547838381226077</v>
+        <v>3.612298916466762</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.274463691452191</v>
+        <v>2.228974417623147</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1472082232969988</v>
+        <v>0.14721651368562</v>
       </c>
       <c r="C52">
-        <v>9.803687232635454</v>
+        <v>9.591275317551963</v>
       </c>
       <c r="D52">
-        <v>16.04868723263546</v>
+        <v>16.04737531755196</v>
       </c>
       <c r="E52">
-        <v>1.145</v>
+        <v>1.3561</v>
       </c>
       <c r="F52">
-        <v>10.555</v>
+        <v>10.7661</v>
       </c>
       <c r="G52">
         <v>4.31</v>
@@ -5545,28 +5545,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M52">
-        <v>0.800069</v>
+        <v>0.8160703800000001</v>
       </c>
       <c r="N52">
-        <v>0.9832643333333334</v>
+        <v>0.9672629533333333</v>
       </c>
       <c r="O52">
-        <v>0.162238615</v>
+        <v>0.1595983873</v>
       </c>
       <c r="P52">
-        <v>0.8210257183333334</v>
+        <v>0.8076645660333334</v>
       </c>
       <c r="Q52">
-        <v>1.971025718333334</v>
+        <v>1.957664566033333</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2311234465939975</v>
+        <v>0.2345654769094285</v>
       </c>
       <c r="T52">
-        <v>3.612298916466762</v>
+        <v>3.679390493962168</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.228974417623147</v>
+        <v>2.185269036885438</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.14721651368562</v>
+        <v>0.1472248040742412</v>
       </c>
       <c r="C53">
-        <v>9.591275317551963</v>
+        <v>9.378863616938421</v>
       </c>
       <c r="D53">
-        <v>16.04737531755196</v>
+        <v>16.04606361693842</v>
       </c>
       <c r="E53">
-        <v>1.3561</v>
+        <v>1.5672</v>
       </c>
       <c r="F53">
-        <v>10.7661</v>
+        <v>10.9772</v>
       </c>
       <c r="G53">
         <v>4.31</v>
@@ -5627,28 +5627,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M53">
-        <v>0.8160703800000001</v>
+        <v>0.83207176</v>
       </c>
       <c r="N53">
-        <v>0.9672629533333333</v>
+        <v>0.9512615733333334</v>
       </c>
       <c r="O53">
-        <v>0.1595983873</v>
+        <v>0.1569581596</v>
       </c>
       <c r="P53">
-        <v>0.8076645660333334</v>
+        <v>0.7943034137333334</v>
       </c>
       <c r="Q53">
-        <v>1.957664566033333</v>
+        <v>1.944303413733333</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2345654769094285</v>
+        <v>0.2381509251546691</v>
       </c>
       <c r="T53">
-        <v>3.679390493962168</v>
+        <v>3.749277553853217</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.185269036885438</v>
+        <v>2.143244632329949</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1472248040742412</v>
+        <v>0.1472330944628624</v>
       </c>
       <c r="C54">
-        <v>9.378863616938421</v>
+        <v>9.166452130742231</v>
       </c>
       <c r="D54">
-        <v>16.04606361693842</v>
+        <v>16.04475213074223</v>
       </c>
       <c r="E54">
-        <v>1.5672</v>
+        <v>1.7783</v>
       </c>
       <c r="F54">
-        <v>10.9772</v>
+        <v>11.1883</v>
       </c>
       <c r="G54">
         <v>4.31</v>
@@ -5709,28 +5709,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M54">
-        <v>0.83207176</v>
+        <v>0.8480731400000001</v>
       </c>
       <c r="N54">
-        <v>0.9512615733333334</v>
+        <v>0.9352601933333333</v>
       </c>
       <c r="O54">
-        <v>0.1569581596</v>
+        <v>0.1543179319</v>
       </c>
       <c r="P54">
-        <v>0.7943034137333334</v>
+        <v>0.7809422614333333</v>
       </c>
       <c r="Q54">
-        <v>1.944303413733333</v>
+        <v>1.930942261433334</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2381509251546691</v>
+        <v>0.2418889456656646</v>
       </c>
       <c r="T54">
-        <v>3.749277553853217</v>
+        <v>3.822138531186438</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.143244632329949</v>
+        <v>2.102806054361459</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1472330944628624</v>
+        <v>0.1472413848514836</v>
       </c>
       <c r="C55">
-        <v>9.166452130742231</v>
+        <v>8.954040858910826</v>
       </c>
       <c r="D55">
-        <v>16.04475213074223</v>
+        <v>16.04344085891083</v>
       </c>
       <c r="E55">
-        <v>1.7783</v>
+        <v>1.9894</v>
       </c>
       <c r="F55">
-        <v>11.1883</v>
+        <v>11.3994</v>
       </c>
       <c r="G55">
         <v>4.31</v>
@@ -5791,28 +5791,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M55">
-        <v>0.8480731400000001</v>
+        <v>0.8640745200000001</v>
       </c>
       <c r="N55">
-        <v>0.9352601933333333</v>
+        <v>0.9192588133333334</v>
       </c>
       <c r="O55">
-        <v>0.1543179319</v>
+        <v>0.1516777042</v>
       </c>
       <c r="P55">
-        <v>0.7809422614333333</v>
+        <v>0.7675811091333333</v>
       </c>
       <c r="Q55">
-        <v>1.930942261433334</v>
+        <v>1.917581109133333</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2418889456656646</v>
+        <v>0.245789488807573</v>
       </c>
       <c r="T55">
-        <v>3.822138531186438</v>
+        <v>3.898167377099364</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.102806054361459</v>
+        <v>2.063865201502914</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1472413848514836</v>
+        <v>0.1472496752401048</v>
       </c>
       <c r="C56">
-        <v>8.954040858910826</v>
+        <v>8.741629801391644</v>
       </c>
       <c r="D56">
-        <v>16.04344085891083</v>
+        <v>16.04212980139165</v>
       </c>
       <c r="E56">
-        <v>1.9894</v>
+        <v>2.2005</v>
       </c>
       <c r="F56">
-        <v>11.3994</v>
+        <v>11.6105</v>
       </c>
       <c r="G56">
         <v>4.31</v>
@@ -5873,28 +5873,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M56">
-        <v>0.8640745200000001</v>
+        <v>0.8800759</v>
       </c>
       <c r="N56">
-        <v>0.9192588133333334</v>
+        <v>0.9032574333333334</v>
       </c>
       <c r="O56">
-        <v>0.1516777042</v>
+        <v>0.1490374765</v>
       </c>
       <c r="P56">
-        <v>0.7675811091333333</v>
+        <v>0.7542199568333334</v>
       </c>
       <c r="Q56">
-        <v>1.917581109133333</v>
+        <v>1.904219956833334</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.245789488807573</v>
+        <v>0.2498633894224551</v>
       </c>
       <c r="T56">
-        <v>3.898167377099364</v>
+        <v>3.977575282830644</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.063865201502914</v>
+        <v>2.026340379657406</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1472496752401048</v>
+        <v>0.1538978856287259</v>
       </c>
       <c r="C57">
-        <v>8.741629801391644</v>
+        <v>7.543910559202882</v>
       </c>
       <c r="D57">
-        <v>16.04212980139165</v>
+        <v>15.05551055920288</v>
       </c>
       <c r="E57">
-        <v>2.2005</v>
+        <v>2.4116</v>
       </c>
       <c r="F57">
-        <v>11.6105</v>
+        <v>11.8216</v>
       </c>
       <c r="G57">
         <v>4.31</v>
@@ -5955,45 +5955,45 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M57">
-        <v>0.8800759</v>
+        <v>1.063944</v>
       </c>
       <c r="N57">
-        <v>0.9032574333333334</v>
+        <v>0.7193893333333334</v>
       </c>
       <c r="O57">
-        <v>0.1490374765</v>
+        <v>0.11869924</v>
       </c>
       <c r="P57">
-        <v>0.7542199568333334</v>
+        <v>0.6006900933333335</v>
       </c>
       <c r="Q57">
-        <v>1.904219956833334</v>
+        <v>1.750690093333334</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2498633894224551</v>
+        <v>0.2541224673380135</v>
       </c>
       <c r="T57">
-        <v>3.977575282830644</v>
+        <v>4.060592638822433</v>
       </c>
       <c r="U57">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V57">
         <v>0.165</v>
       </c>
       <c r="W57">
-        <v>0.063293</v>
+        <v>0.07514999999999999</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y57">
-        <v>2.026340379657406</v>
+        <v>1.676153381506295</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1538978856287259</v>
+        <v>0.1540247460173471</v>
       </c>
       <c r="C58">
-        <v>7.543910559202882</v>
+        <v>7.315162581353851</v>
       </c>
       <c r="D58">
-        <v>15.05551055920288</v>
+        <v>15.03786258135385</v>
       </c>
       <c r="E58">
-        <v>2.4116</v>
+        <v>2.6227</v>
       </c>
       <c r="F58">
-        <v>11.8216</v>
+        <v>12.0327</v>
       </c>
       <c r="G58">
         <v>4.31</v>
@@ -6037,28 +6037,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M58">
-        <v>1.063944</v>
+        <v>1.082943</v>
       </c>
       <c r="N58">
-        <v>0.7193893333333334</v>
+        <v>0.7003903333333334</v>
       </c>
       <c r="O58">
-        <v>0.11869924</v>
+        <v>0.115564405</v>
       </c>
       <c r="P58">
-        <v>0.6006900933333335</v>
+        <v>0.5848259283333335</v>
       </c>
       <c r="Q58">
-        <v>1.750690093333334</v>
+        <v>1.734825928333334</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2541224673380135</v>
+        <v>0.2585796419008073</v>
       </c>
       <c r="T58">
-        <v>4.060592638822433</v>
+        <v>4.147471267185936</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.676153381506295</v>
+        <v>1.646747181830746</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1540247460173471</v>
+        <v>0.1541516064059683</v>
       </c>
       <c r="C59">
-        <v>7.315162581353851</v>
+        <v>7.086455928768055</v>
       </c>
       <c r="D59">
-        <v>15.03786258135385</v>
+        <v>15.02025592876806</v>
       </c>
       <c r="E59">
-        <v>2.6227</v>
+        <v>2.833800000000002</v>
       </c>
       <c r="F59">
-        <v>12.0327</v>
+        <v>12.2438</v>
       </c>
       <c r="G59">
         <v>4.31</v>
@@ -6119,28 +6119,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M59">
-        <v>1.082943</v>
+        <v>1.101942</v>
       </c>
       <c r="N59">
-        <v>0.7003903333333334</v>
+        <v>0.6813913333333332</v>
       </c>
       <c r="O59">
-        <v>0.115564405</v>
+        <v>0.11242957</v>
       </c>
       <c r="P59">
-        <v>0.5848259283333335</v>
+        <v>0.5689617633333333</v>
       </c>
       <c r="Q59">
-        <v>1.734825928333334</v>
+        <v>1.718961763333333</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2585796419008073</v>
+        <v>0.2632490628713532</v>
       </c>
       <c r="T59">
-        <v>4.147471267185936</v>
+        <v>4.238486973090557</v>
       </c>
       <c r="U59">
         <v>0.09</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.646747181830746</v>
+        <v>1.61835498904056</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1541516064059684</v>
+        <v>0.1542784667945896</v>
       </c>
       <c r="C60">
-        <v>7.086455928768055</v>
+        <v>6.857790456461728</v>
       </c>
       <c r="D60">
-        <v>15.02025592876806</v>
+        <v>15.00269045646173</v>
       </c>
       <c r="E60">
-        <v>2.833799999999998</v>
+        <v>3.044899999999998</v>
       </c>
       <c r="F60">
-        <v>12.2438</v>
+        <v>12.4549</v>
       </c>
       <c r="G60">
         <v>4.31</v>
@@ -6201,28 +6201,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M60">
-        <v>1.101942</v>
+        <v>1.120941</v>
       </c>
       <c r="N60">
-        <v>0.6813913333333337</v>
+        <v>0.6623923333333337</v>
       </c>
       <c r="O60">
-        <v>0.1124295700000001</v>
+        <v>0.1092947350000001</v>
       </c>
       <c r="P60">
-        <v>0.5689617633333336</v>
+        <v>0.5530975983333336</v>
       </c>
       <c r="Q60">
-        <v>1.718961763333334</v>
+        <v>1.703097598333334</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2632490628713532</v>
+        <v>0.2681462604746087</v>
       </c>
       <c r="T60">
-        <v>4.238486973090557</v>
+        <v>4.333942469527111</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.618354989040561</v>
+        <v>1.590925243463602</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1542784667945896</v>
+        <v>0.1544053271832108</v>
       </c>
       <c r="C61">
-        <v>6.857790456461728</v>
+        <v>6.62916602012851</v>
       </c>
       <c r="D61">
-        <v>15.00269045646173</v>
+        <v>14.98516602012851</v>
       </c>
       <c r="E61">
-        <v>3.044899999999998</v>
+        <v>3.255999999999998</v>
       </c>
       <c r="F61">
-        <v>12.4549</v>
+        <v>12.666</v>
       </c>
       <c r="G61">
         <v>4.31</v>
@@ -6283,28 +6283,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M61">
-        <v>1.120941</v>
+        <v>1.13994</v>
       </c>
       <c r="N61">
-        <v>0.6623923333333337</v>
+        <v>0.6433933333333337</v>
       </c>
       <c r="O61">
-        <v>0.1092947350000001</v>
+        <v>0.1061599000000001</v>
       </c>
       <c r="P61">
-        <v>0.5530975983333336</v>
+        <v>0.5372334333333336</v>
       </c>
       <c r="Q61">
-        <v>1.703097598333334</v>
+        <v>1.687233433333334</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2681462604746087</v>
+        <v>0.2732883179580269</v>
       </c>
       <c r="T61">
-        <v>4.333942469527111</v>
+        <v>4.434170740785492</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.590925243463602</v>
+        <v>1.564409822739209</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1544053271832108</v>
+        <v>0.154532187571832</v>
       </c>
       <c r="C62">
-        <v>6.62916602012851</v>
+        <v>6.400582476135519</v>
       </c>
       <c r="D62">
-        <v>14.98516602012851</v>
+        <v>14.96768247613552</v>
       </c>
       <c r="E62">
-        <v>3.255999999999998</v>
+        <v>3.467099999999999</v>
       </c>
       <c r="F62">
-        <v>12.666</v>
+        <v>12.8771</v>
       </c>
       <c r="G62">
         <v>4.31</v>
@@ -6365,28 +6365,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M62">
-        <v>1.13994</v>
+        <v>1.158939</v>
       </c>
       <c r="N62">
-        <v>0.6433933333333337</v>
+        <v>0.6243943333333335</v>
       </c>
       <c r="O62">
-        <v>0.1061599000000001</v>
+        <v>0.103025065</v>
       </c>
       <c r="P62">
-        <v>0.5372334333333336</v>
+        <v>0.5213692683333335</v>
       </c>
       <c r="Q62">
-        <v>1.687233433333334</v>
+        <v>1.671369268333334</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2732883179580269</v>
+        <v>0.2786940706970051</v>
       </c>
       <c r="T62">
-        <v>4.434170740785492</v>
+        <v>4.53953892339046</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.564409822739209</v>
+        <v>1.538763760071353</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.154532187571832</v>
+        <v>0.1546590479604532</v>
       </c>
       <c r="C63">
-        <v>6.400582476135519</v>
+        <v>6.172039681519388</v>
       </c>
       <c r="D63">
-        <v>14.96768247613552</v>
+        <v>14.95023968151939</v>
       </c>
       <c r="E63">
-        <v>3.467099999999999</v>
+        <v>3.678199999999999</v>
       </c>
       <c r="F63">
-        <v>12.8771</v>
+        <v>13.0882</v>
       </c>
       <c r="G63">
         <v>4.31</v>
@@ -6447,28 +6447,28 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M63">
-        <v>1.158939</v>
+        <v>1.177938</v>
       </c>
       <c r="N63">
-        <v>0.6243943333333335</v>
+        <v>0.6053953333333335</v>
       </c>
       <c r="O63">
-        <v>0.103025065</v>
+        <v>0.09989023000000004</v>
       </c>
       <c r="P63">
-        <v>0.5213692683333335</v>
+        <v>0.5055051033333334</v>
       </c>
       <c r="Q63">
-        <v>1.671369268333334</v>
+        <v>1.655505103333334</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2786940706970051</v>
+        <v>0.2843843367380346</v>
       </c>
       <c r="T63">
-        <v>4.53953892339046</v>
+        <v>4.650452799816739</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.538763760071353</v>
+        <v>1.513944989747621</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1546590479604532</v>
+        <v>0.1868953008844907</v>
       </c>
       <c r="C64">
-        <v>6.172039681519388</v>
+        <v>2.545236219906682</v>
       </c>
       <c r="D64">
-        <v>14.95023968151939</v>
+        <v>11.53453621990668</v>
       </c>
       <c r="E64">
-        <v>3.678199999999999</v>
+        <v>3.8893</v>
       </c>
       <c r="F64">
-        <v>13.0882</v>
+        <v>13.2993</v>
       </c>
       <c r="G64">
         <v>4.31</v>
@@ -6529,45 +6529,45 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M64">
-        <v>1.177938</v>
+        <v>1.95233724</v>
       </c>
       <c r="N64">
-        <v>0.6053953333333335</v>
+        <v>-0.1690039066666669</v>
       </c>
       <c r="O64">
-        <v>0.09989023000000004</v>
+        <v>-0.02788564460000003</v>
       </c>
       <c r="P64">
-        <v>0.5055051033333334</v>
+        <v>-0.1411182620666668</v>
       </c>
       <c r="Q64">
-        <v>1.655505103333334</v>
+        <v>1.008881737933333</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2843843367380346</v>
+        <v>0.2928383578516135</v>
       </c>
       <c r="T64">
-        <v>4.650452799816739</v>
+        <v>4.815237406781614</v>
       </c>
       <c r="U64">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.165</v>
+        <v>0.1507167890727731</v>
       </c>
       <c r="W64">
-        <v>0.07514999999999999</v>
+        <v>0.1246747753641169</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y64">
-        <v>1.513944989747621</v>
+        <v>0.9134350852895339</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1868953008844907</v>
+        <v>0.1879053008844906</v>
       </c>
       <c r="C65">
-        <v>2.545236219906682</v>
+        <v>2.25215559350081</v>
       </c>
       <c r="D65">
-        <v>11.53453621990668</v>
+        <v>11.45255559350081</v>
       </c>
       <c r="E65">
-        <v>3.8893</v>
+        <v>4.1004</v>
       </c>
       <c r="F65">
-        <v>13.2993</v>
+        <v>13.5104</v>
       </c>
       <c r="G65">
         <v>4.31</v>
@@ -6611,37 +6611,37 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M65">
-        <v>1.95233724</v>
+        <v>1.98332672</v>
       </c>
       <c r="N65">
-        <v>-0.1690039066666669</v>
+        <v>-0.1999933866666668</v>
       </c>
       <c r="O65">
-        <v>-0.02788564460000003</v>
+        <v>-0.03299890880000002</v>
       </c>
       <c r="P65">
-        <v>-0.1411182620666668</v>
+        <v>-0.1669944778666668</v>
       </c>
       <c r="Q65">
-        <v>1.008881737933333</v>
+        <v>0.9830055221333334</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2928383578516135</v>
+        <v>0.2997005344586028</v>
       </c>
       <c r="T65">
-        <v>4.815237406781614</v>
+        <v>4.948994001414437</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.1507167890727731</v>
+        <v>0.148361839243511</v>
       </c>
       <c r="W65">
-        <v>0.1246747753641169</v>
+        <v>0.1250204819990526</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.9134350852895339</v>
+        <v>0.8991626620818849</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1879053008844906</v>
+        <v>0.1889153008844907</v>
       </c>
       <c r="C66">
-        <v>2.25215559350081</v>
+        <v>1.960232082122586</v>
       </c>
       <c r="D66">
-        <v>11.45255559350081</v>
+        <v>11.37173208212259</v>
       </c>
       <c r="E66">
-        <v>4.1004</v>
+        <v>4.311500000000001</v>
       </c>
       <c r="F66">
-        <v>13.5104</v>
+        <v>13.7215</v>
       </c>
       <c r="G66">
         <v>4.31</v>
@@ -6693,37 +6693,37 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M66">
-        <v>1.98332672</v>
+        <v>2.0143162</v>
       </c>
       <c r="N66">
-        <v>-0.1999933866666668</v>
+        <v>-0.2309828666666667</v>
       </c>
       <c r="O66">
-        <v>-0.03299890880000002</v>
+        <v>-0.03811217300000001</v>
       </c>
       <c r="P66">
-        <v>-0.1669944778666668</v>
+        <v>-0.1928706936666667</v>
       </c>
       <c r="Q66">
-        <v>0.9830055221333334</v>
+        <v>0.9571293063333335</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2997005344586028</v>
+        <v>0.3069548354431343</v>
       </c>
       <c r="T66">
-        <v>4.948994001414437</v>
+        <v>5.090393830026278</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.148361839243511</v>
+        <v>0.1460793494089955</v>
       </c>
       <c r="W66">
-        <v>0.1250204819990526</v>
+        <v>0.1253555515067595</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8991626620818849</v>
+        <v>0.8853293903575483</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1889153008844907</v>
+        <v>0.1899253008844906</v>
       </c>
       <c r="C67">
-        <v>1.960232082122586</v>
+        <v>1.669441359310849</v>
       </c>
       <c r="D67">
-        <v>11.37173208212259</v>
+        <v>11.29204135931085</v>
       </c>
       <c r="E67">
-        <v>4.311500000000001</v>
+        <v>4.522600000000001</v>
       </c>
       <c r="F67">
-        <v>13.7215</v>
+        <v>13.9326</v>
       </c>
       <c r="G67">
         <v>4.31</v>
@@ -6775,37 +6775,37 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M67">
-        <v>2.0143162</v>
+        <v>2.04530568</v>
       </c>
       <c r="N67">
-        <v>-0.2309828666666667</v>
+        <v>-0.2619723466666668</v>
       </c>
       <c r="O67">
-        <v>-0.03811217300000001</v>
+        <v>-0.04322543720000002</v>
       </c>
       <c r="P67">
-        <v>-0.1928706936666667</v>
+        <v>-0.2187469094666668</v>
       </c>
       <c r="Q67">
-        <v>0.9571293063333335</v>
+        <v>0.9312530905333334</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3069548354431343</v>
+        <v>0.3146358600149912</v>
       </c>
       <c r="T67">
-        <v>5.090393830026278</v>
+        <v>5.240111295615286</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.1460793494089955</v>
+        <v>0.1438660259331016</v>
       </c>
       <c r="W67">
-        <v>0.1253555515067595</v>
+        <v>0.1256804673930207</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8853293903575483</v>
+        <v>0.8719153086854642</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1899253008844906</v>
+        <v>0.1909353008844907</v>
       </c>
       <c r="C68">
-        <v>1.669441359310849</v>
+        <v>1.379759775758126</v>
       </c>
       <c r="D68">
-        <v>11.29204135931085</v>
+        <v>11.21345977575813</v>
       </c>
       <c r="E68">
-        <v>4.522600000000001</v>
+        <v>4.733700000000001</v>
       </c>
       <c r="F68">
-        <v>13.9326</v>
+        <v>14.1437</v>
       </c>
       <c r="G68">
         <v>4.31</v>
@@ -6857,37 +6857,37 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M68">
-        <v>2.04530568</v>
+        <v>2.07629516</v>
       </c>
       <c r="N68">
-        <v>-0.2619723466666668</v>
+        <v>-0.2929618266666669</v>
       </c>
       <c r="O68">
-        <v>-0.04322543720000002</v>
+        <v>-0.04833870140000004</v>
       </c>
       <c r="P68">
-        <v>-0.2187469094666668</v>
+        <v>-0.2446231252666669</v>
       </c>
       <c r="Q68">
-        <v>0.9312530905333334</v>
+        <v>0.9053768747333333</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3146358600149912</v>
+        <v>0.3227824012275667</v>
       </c>
       <c r="T68">
-        <v>5.240111295615286</v>
+        <v>5.398902546997568</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.1438660259331016</v>
+        <v>0.1417187718146971</v>
       </c>
       <c r="W68">
-        <v>0.1256804673930207</v>
+        <v>0.1259956842976025</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8719153086854642</v>
+        <v>0.8589016473618005</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1909353008844907</v>
+        <v>0.1919453008844907</v>
       </c>
       <c r="C69">
-        <v>1.379759775758126</v>
+        <v>1.09116433591181</v>
       </c>
       <c r="D69">
-        <v>11.21345977575813</v>
+        <v>11.13596433591181</v>
       </c>
       <c r="E69">
-        <v>4.733700000000001</v>
+        <v>4.944800000000001</v>
       </c>
       <c r="F69">
-        <v>14.1437</v>
+        <v>14.3548</v>
       </c>
       <c r="G69">
         <v>4.31</v>
@@ -6939,37 +6939,37 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M69">
-        <v>2.07629516</v>
+        <v>2.10728464</v>
       </c>
       <c r="N69">
-        <v>-0.2929618266666669</v>
+        <v>-0.323951306666667</v>
       </c>
       <c r="O69">
-        <v>-0.04833870140000004</v>
+        <v>-0.05345196560000007</v>
       </c>
       <c r="P69">
-        <v>-0.2446231252666669</v>
+        <v>-0.270499341066667</v>
       </c>
       <c r="Q69">
-        <v>0.9053768747333333</v>
+        <v>0.8795006589333332</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3227824012275667</v>
+        <v>0.3314381012659282</v>
       </c>
       <c r="T69">
-        <v>5.398902546997568</v>
+        <v>5.567618251591243</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.1417187718146971</v>
+        <v>0.1396346722291868</v>
       </c>
       <c r="W69">
-        <v>0.1259956842976025</v>
+        <v>0.1263016301167554</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8589016473618005</v>
+        <v>0.8462707407829504</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1919453008844907</v>
+        <v>0.1929553008844907</v>
       </c>
       <c r="C70">
-        <v>1.09116433591181</v>
+        <v>0.8036326755389407</v>
       </c>
       <c r="D70">
-        <v>11.13596433591181</v>
+        <v>11.05953267553894</v>
       </c>
       <c r="E70">
-        <v>4.944800000000001</v>
+        <v>5.155900000000001</v>
       </c>
       <c r="F70">
-        <v>14.3548</v>
+        <v>14.5659</v>
       </c>
       <c r="G70">
         <v>4.31</v>
@@ -7021,37 +7021,37 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M70">
-        <v>2.10728464</v>
+        <v>2.13827412</v>
       </c>
       <c r="N70">
-        <v>-0.323951306666667</v>
+        <v>-0.3549407866666667</v>
       </c>
       <c r="O70">
-        <v>-0.05345196560000007</v>
+        <v>-0.05856522980000001</v>
       </c>
       <c r="P70">
-        <v>-0.270499341066667</v>
+        <v>-0.2963755568666667</v>
       </c>
       <c r="Q70">
-        <v>0.8795006589333332</v>
+        <v>0.8536244431333334</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3314381012659282</v>
+        <v>0.3406522335648291</v>
       </c>
       <c r="T70">
-        <v>5.567618251591243</v>
+        <v>5.74721884035225</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.1396346722291868</v>
+        <v>0.1376109813273146</v>
       </c>
       <c r="W70">
-        <v>0.1263016301167554</v>
+        <v>0.1265987079411502</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8462707407829504</v>
+        <v>0.8340059474382702</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1929553008844907</v>
+        <v>0.1939653008844907</v>
       </c>
       <c r="C71">
-        <v>0.8036326755389407</v>
+        <v>0.5171430402085839</v>
       </c>
       <c r="D71">
-        <v>11.05953267553894</v>
+        <v>10.98414304020859</v>
       </c>
       <c r="E71">
-        <v>5.155900000000001</v>
+        <v>5.367000000000001</v>
       </c>
       <c r="F71">
-        <v>14.5659</v>
+        <v>14.777</v>
       </c>
       <c r="G71">
         <v>4.31</v>
@@ -7103,37 +7103,37 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M71">
-        <v>2.13827412</v>
+        <v>2.1692636</v>
       </c>
       <c r="N71">
-        <v>-0.3549407866666667</v>
+        <v>-0.3859302666666669</v>
       </c>
       <c r="O71">
-        <v>-0.05856522980000001</v>
+        <v>-0.06367849400000003</v>
       </c>
       <c r="P71">
-        <v>-0.2963755568666667</v>
+        <v>-0.3222517726666668</v>
       </c>
       <c r="Q71">
-        <v>0.8536244431333334</v>
+        <v>0.8277482273333333</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3406522335648291</v>
+        <v>0.3504806413503234</v>
       </c>
       <c r="T71">
-        <v>5.74721884035225</v>
+        <v>5.938792801697326</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.1376109813273146</v>
+        <v>0.1356451101654958</v>
       </c>
       <c r="W71">
-        <v>0.1265987079411502</v>
+        <v>0.1268872978277052</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8340059474382702</v>
+        <v>0.8220915767605805</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1939653008844907</v>
+        <v>0.1949753008844907</v>
       </c>
       <c r="C72">
-        <v>0.5171430402085839</v>
+        <v>0.2316742646483387</v>
       </c>
       <c r="D72">
-        <v>10.98414304020859</v>
+        <v>10.90977426464834</v>
       </c>
       <c r="E72">
-        <v>5.367000000000001</v>
+        <v>5.578100000000001</v>
       </c>
       <c r="F72">
-        <v>14.777</v>
+        <v>14.9881</v>
       </c>
       <c r="G72">
         <v>4.31</v>
@@ -7185,37 +7185,37 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M72">
-        <v>2.1692636</v>
+        <v>2.20025308</v>
       </c>
       <c r="N72">
-        <v>-0.3859302666666669</v>
+        <v>-0.416919746666667</v>
       </c>
       <c r="O72">
-        <v>-0.06367849400000003</v>
+        <v>-0.06879175820000005</v>
       </c>
       <c r="P72">
-        <v>-0.3222517726666668</v>
+        <v>-0.3481279884666669</v>
       </c>
       <c r="Q72">
-        <v>0.8277482273333333</v>
+        <v>0.8018720115333332</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3504806413503234</v>
+        <v>0.3609868703624036</v>
       </c>
       <c r="T72">
-        <v>5.938792801697326</v>
+        <v>6.143578760376545</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.1356451101654958</v>
+        <v>0.1337346156561226</v>
       </c>
       <c r="W72">
-        <v>0.1268872978277052</v>
+        <v>0.1271677584216812</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8220915767605805</v>
+        <v>0.8105128221583188</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1949753008844907</v>
+        <v>0.2374441535681832</v>
       </c>
       <c r="C73">
-        <v>0.2316742646483405</v>
+        <v>-2.397060645841366</v>
       </c>
       <c r="D73">
-        <v>10.90977426464834</v>
+        <v>8.492139354158635</v>
       </c>
       <c r="E73">
-        <v>5.578099999999999</v>
+        <v>5.789199999999999</v>
       </c>
       <c r="F73">
-        <v>14.9881</v>
+        <v>15.1992</v>
       </c>
       <c r="G73">
         <v>4.31</v>
@@ -7267,45 +7267,45 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M73">
-        <v>2.20025308</v>
+        <v>3.05199936</v>
       </c>
       <c r="N73">
-        <v>-0.4169197466666665</v>
+        <v>-1.268666026666667</v>
       </c>
       <c r="O73">
-        <v>-0.06879175819999998</v>
+        <v>-0.2093298944</v>
       </c>
       <c r="P73">
-        <v>-0.3481279884666665</v>
+        <v>-1.059336132266667</v>
       </c>
       <c r="Q73">
-        <v>0.8018720115333335</v>
+        <v>0.09066386773333357</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3609868703624035</v>
+        <v>0.3814537324599624</v>
       </c>
       <c r="T73">
-        <v>6.143578760376542</v>
+        <v>6.542515997608356</v>
       </c>
       <c r="U73">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.1337346156561226</v>
+        <v>0.09641220894620373</v>
       </c>
       <c r="W73">
-        <v>0.1271677584216812</v>
+        <v>0.1814404284436023</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y73">
-        <v>0.8105128221583189</v>
+        <v>0.58431641785578</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2374441535681832</v>
+        <v>0.2389941535681832</v>
       </c>
       <c r="C74">
-        <v>-2.397060645841366</v>
+        <v>-2.67629322519657</v>
       </c>
       <c r="D74">
-        <v>8.492139354158635</v>
+        <v>8.424006774803431</v>
       </c>
       <c r="E74">
-        <v>5.789199999999999</v>
+        <v>6.000299999999999</v>
       </c>
       <c r="F74">
-        <v>15.1992</v>
+        <v>15.4103</v>
       </c>
       <c r="G74">
         <v>4.31</v>
@@ -7349,37 +7349,37 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M74">
-        <v>3.05199936</v>
+        <v>3.09438824</v>
       </c>
       <c r="N74">
-        <v>-1.268666026666667</v>
+        <v>-1.311054906666666</v>
       </c>
       <c r="O74">
-        <v>-0.2093298944</v>
+        <v>-0.2163240596</v>
       </c>
       <c r="P74">
-        <v>-1.059336132266667</v>
+        <v>-1.094730847066666</v>
       </c>
       <c r="Q74">
-        <v>0.09066386773333357</v>
+        <v>0.05526915293333379</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3814537324599624</v>
+        <v>0.3938853521807018</v>
       </c>
       <c r="T74">
-        <v>6.542515997608356</v>
+        <v>6.784831404927184</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.09641220894620373</v>
+        <v>0.09509149375515984</v>
       </c>
       <c r="W74">
-        <v>0.1814404284436023</v>
+        <v>0.1817056280539639</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.58431641785578</v>
+        <v>0.576312083364605</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2389941535681832</v>
+        <v>0.2405441535681831</v>
       </c>
       <c r="C75">
-        <v>-2.67629322519657</v>
+        <v>-2.954441248265328</v>
       </c>
       <c r="D75">
-        <v>8.424006774803431</v>
+        <v>8.356958751734672</v>
       </c>
       <c r="E75">
-        <v>6.000299999999999</v>
+        <v>6.211399999999999</v>
       </c>
       <c r="F75">
-        <v>15.4103</v>
+        <v>15.6214</v>
       </c>
       <c r="G75">
         <v>4.31</v>
@@ -7431,37 +7431,37 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M75">
-        <v>3.09438824</v>
+        <v>3.13677712</v>
       </c>
       <c r="N75">
-        <v>-1.311054906666666</v>
+        <v>-1.353443786666667</v>
       </c>
       <c r="O75">
-        <v>-0.2163240596</v>
+        <v>-0.2233182248</v>
       </c>
       <c r="P75">
-        <v>-1.094730847066666</v>
+        <v>-1.130125561866667</v>
       </c>
       <c r="Q75">
-        <v>0.05526915293333379</v>
+        <v>0.01987443813333356</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3938853521807018</v>
+        <v>0.407273250341498</v>
       </c>
       <c r="T75">
-        <v>6.784831404927184</v>
+        <v>7.045786458962845</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.09509149375515984</v>
+        <v>0.09380647356927929</v>
       </c>
       <c r="W75">
-        <v>0.1817056280539639</v>
+        <v>0.1819636601072887</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.576312083364605</v>
+        <v>0.5685240822380563</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2405441535681831</v>
+        <v>0.2420941535681831</v>
       </c>
       <c r="C76">
-        <v>-2.954441248265328</v>
+        <v>-3.231530407034082</v>
       </c>
       <c r="D76">
-        <v>8.356958751734672</v>
+        <v>8.290969592965919</v>
       </c>
       <c r="E76">
-        <v>6.211399999999999</v>
+        <v>6.422499999999999</v>
       </c>
       <c r="F76">
-        <v>15.6214</v>
+        <v>15.8325</v>
       </c>
       <c r="G76">
         <v>4.31</v>
@@ -7513,37 +7513,37 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M76">
-        <v>3.13677712</v>
+        <v>3.179166</v>
       </c>
       <c r="N76">
-        <v>-1.353443786666667</v>
+        <v>-1.395832666666666</v>
       </c>
       <c r="O76">
-        <v>-0.2233182248</v>
+        <v>-0.23031239</v>
       </c>
       <c r="P76">
-        <v>-1.130125561866667</v>
+        <v>-1.165520276666667</v>
       </c>
       <c r="Q76">
-        <v>0.01987443813333356</v>
+        <v>-0.01552027666666644</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.407273250341498</v>
+        <v>0.421732180355158</v>
       </c>
       <c r="T76">
-        <v>7.045786458962845</v>
+        <v>7.327617917321359</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.09380647356927929</v>
+        <v>0.09255572058835557</v>
       </c>
       <c r="W76">
-        <v>0.1819636601072887</v>
+        <v>0.1822148113058582</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5685240822380563</v>
+        <v>0.5609437611415489</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2420941535681831</v>
+        <v>0.2436441535681831</v>
       </c>
       <c r="C77">
-        <v>-3.231530407034082</v>
+        <v>-3.507585588359003</v>
       </c>
       <c r="D77">
-        <v>8.290969592965919</v>
+        <v>8.226014411640998</v>
       </c>
       <c r="E77">
-        <v>6.422499999999999</v>
+        <v>6.633600000000001</v>
       </c>
       <c r="F77">
-        <v>15.8325</v>
+        <v>16.0436</v>
       </c>
       <c r="G77">
         <v>4.31</v>
@@ -7595,37 +7595,37 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M77">
-        <v>3.179166</v>
+        <v>3.22155488</v>
       </c>
       <c r="N77">
-        <v>-1.395832666666666</v>
+        <v>-1.438221546666667</v>
       </c>
       <c r="O77">
-        <v>-0.23031239</v>
+        <v>-0.2373065552</v>
       </c>
       <c r="P77">
-        <v>-1.165520276666667</v>
+        <v>-1.200914991466667</v>
       </c>
       <c r="Q77">
-        <v>-0.01552027666666644</v>
+        <v>-0.05091499146666667</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.421732180355158</v>
+        <v>0.4373960212032896</v>
       </c>
       <c r="T77">
-        <v>7.327617917321359</v>
+        <v>7.632935330543084</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.09255572058835557</v>
+        <v>0.09133788215956141</v>
       </c>
       <c r="W77">
-        <v>0.1822148113058582</v>
+        <v>0.1824593532623601</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5609437611415489</v>
+        <v>0.55356292217916</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2436441535681831</v>
+        <v>0.2451941535681831</v>
       </c>
       <c r="C78">
-        <v>-3.507585588359003</v>
+        <v>-3.782630905259598</v>
       </c>
       <c r="D78">
-        <v>8.226014411640998</v>
+        <v>8.162069094740401</v>
       </c>
       <c r="E78">
-        <v>6.633600000000001</v>
+        <v>6.8447</v>
       </c>
       <c r="F78">
-        <v>16.0436</v>
+        <v>16.2547</v>
       </c>
       <c r="G78">
         <v>4.31</v>
@@ -7677,37 +7677,37 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M78">
-        <v>3.22155488</v>
+        <v>3.26394376</v>
       </c>
       <c r="N78">
-        <v>-1.438221546666667</v>
+        <v>-1.480610426666667</v>
       </c>
       <c r="O78">
-        <v>-0.2373065552</v>
+        <v>-0.2443007204</v>
       </c>
       <c r="P78">
-        <v>-1.200914991466667</v>
+        <v>-1.236309706266667</v>
       </c>
       <c r="Q78">
-        <v>-0.05091499146666667</v>
+        <v>-0.08630970626666645</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4373960212032896</v>
+        <v>0.4544219351686499</v>
       </c>
       <c r="T78">
-        <v>7.632935330543084</v>
+        <v>7.964802084044956</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.09133788215956141</v>
+        <v>0.09015167589774893</v>
       </c>
       <c r="W78">
-        <v>0.1824593532623601</v>
+        <v>0.182697543479732</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.55356292217916</v>
+        <v>0.5463737933196905</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2451941535681831</v>
+        <v>0.2467441535681831</v>
       </c>
       <c r="C79">
-        <v>-3.782630905259598</v>
+        <v>-4.056689726763977</v>
       </c>
       <c r="D79">
-        <v>8.162069094740401</v>
+        <v>8.099110273236024</v>
       </c>
       <c r="E79">
-        <v>6.8447</v>
+        <v>7.055800000000001</v>
       </c>
       <c r="F79">
-        <v>16.2547</v>
+        <v>16.4658</v>
       </c>
       <c r="G79">
         <v>4.31</v>
@@ -7759,37 +7759,37 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M79">
-        <v>3.26394376</v>
+        <v>3.30633264</v>
       </c>
       <c r="N79">
-        <v>-1.480610426666667</v>
+        <v>-1.522999306666667</v>
       </c>
       <c r="O79">
-        <v>-0.2443007204</v>
+        <v>-0.2512948856000001</v>
       </c>
       <c r="P79">
-        <v>-1.236309706266667</v>
+        <v>-1.271704421066667</v>
       </c>
       <c r="Q79">
-        <v>-0.08630970626666645</v>
+        <v>-0.1217044210666667</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4544219351686499</v>
+        <v>0.4729956594944977</v>
       </c>
       <c r="T79">
-        <v>7.964802084044956</v>
+        <v>8.326838542410636</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.09015167589774893</v>
+        <v>0.08899588518111111</v>
       </c>
       <c r="W79">
-        <v>0.182697543479732</v>
+        <v>0.1829296262556329</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5463737933196905</v>
+        <v>0.5393690010976431</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2467441535681831</v>
+        <v>0.2482941535681831</v>
       </c>
       <c r="C80">
-        <v>-4.056689726763977</v>
+        <v>-4.329784706383421</v>
       </c>
       <c r="D80">
-        <v>8.099110273236024</v>
+        <v>8.03711529361658</v>
       </c>
       <c r="E80">
-        <v>7.055800000000001</v>
+        <v>7.2669</v>
       </c>
       <c r="F80">
-        <v>16.4658</v>
+        <v>16.6769</v>
       </c>
       <c r="G80">
         <v>4.31</v>
@@ -7841,37 +7841,37 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M80">
-        <v>3.30633264</v>
+        <v>3.34872152</v>
       </c>
       <c r="N80">
-        <v>-1.522999306666667</v>
+        <v>-1.565388186666667</v>
       </c>
       <c r="O80">
-        <v>-0.2512948856000001</v>
+        <v>-0.2582890508</v>
       </c>
       <c r="P80">
-        <v>-1.271704421066667</v>
+        <v>-1.307099135866667</v>
       </c>
       <c r="Q80">
-        <v>-0.1217044210666667</v>
+        <v>-0.1570991358666667</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4729956594944977</v>
+        <v>0.4933383099466167</v>
       </c>
       <c r="T80">
-        <v>8.326838542410636</v>
+        <v>8.72335466347781</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.08899588518111111</v>
+        <v>0.08786935498894516</v>
       </c>
       <c r="W80">
-        <v>0.1829296262556329</v>
+        <v>0.1831558335182198</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5393690010976431</v>
+        <v>0.5325415453875464</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2482941535681831</v>
+        <v>0.2498441535681832</v>
       </c>
       <c r="C81">
-        <v>-4.329784706383421</v>
+        <v>-4.601937809289129</v>
       </c>
       <c r="D81">
-        <v>8.03711529361658</v>
+        <v>7.976062190710874</v>
       </c>
       <c r="E81">
-        <v>7.2669</v>
+        <v>7.478000000000002</v>
       </c>
       <c r="F81">
-        <v>16.6769</v>
+        <v>16.888</v>
       </c>
       <c r="G81">
         <v>4.31</v>
@@ -7923,37 +7923,37 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M81">
-        <v>3.34872152</v>
+        <v>3.391110400000001</v>
       </c>
       <c r="N81">
-        <v>-1.565388186666667</v>
+        <v>-1.607777066666667</v>
       </c>
       <c r="O81">
-        <v>-0.2582890508</v>
+        <v>-0.2652832160000001</v>
       </c>
       <c r="P81">
-        <v>-1.307099135866667</v>
+        <v>-1.342493850666667</v>
       </c>
       <c r="Q81">
-        <v>-0.1570991358666667</v>
+        <v>-0.1924938506666669</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4933383099466167</v>
+        <v>0.5157152254439475</v>
       </c>
       <c r="T81">
-        <v>8.72335466347781</v>
+        <v>9.159522396651701</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.08786935498894516</v>
+        <v>0.08677098805158334</v>
       </c>
       <c r="W81">
-        <v>0.1831558335182198</v>
+        <v>0.1833763855992421</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5325415453875464</v>
+        <v>0.525884776070202</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2498441535681832</v>
+        <v>0.2513941535681832</v>
       </c>
       <c r="C82">
-        <v>-4.601937809289129</v>
+        <v>-4.873170338259616</v>
       </c>
       <c r="D82">
-        <v>7.976062190710874</v>
+        <v>7.915929661740385</v>
       </c>
       <c r="E82">
-        <v>7.478000000000002</v>
+        <v>7.6891</v>
       </c>
       <c r="F82">
-        <v>16.888</v>
+        <v>17.0991</v>
       </c>
       <c r="G82">
         <v>4.31</v>
@@ -8005,37 +8005,37 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M82">
-        <v>3.391110400000001</v>
+        <v>3.43349928</v>
       </c>
       <c r="N82">
-        <v>-1.607777066666667</v>
+        <v>-1.650165946666666</v>
       </c>
       <c r="O82">
-        <v>-0.2652832160000001</v>
+        <v>-0.2722773812</v>
       </c>
       <c r="P82">
-        <v>-1.342493850666667</v>
+        <v>-1.377888565466666</v>
       </c>
       <c r="Q82">
-        <v>-0.1924938506666669</v>
+        <v>-0.2278885654666662</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5157152254439475</v>
+        <v>0.5404476057304711</v>
       </c>
       <c r="T82">
-        <v>9.159522396651701</v>
+        <v>9.641602522791265</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.08677098805158334</v>
+        <v>0.08569974128551441</v>
       </c>
       <c r="W82">
-        <v>0.1833763855992421</v>
+        <v>0.1835914919498687</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.525884776070202</v>
+        <v>0.5193923714273601</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2513941535681832</v>
+        <v>0.2529441535681831</v>
       </c>
       <c r="C83">
-        <v>-4.873170338259616</v>
+        <v>-5.143502958463202</v>
       </c>
       <c r="D83">
-        <v>7.915929661740385</v>
+        <v>7.8566970415368</v>
       </c>
       <c r="E83">
-        <v>7.6891</v>
+        <v>7.900200000000002</v>
       </c>
       <c r="F83">
-        <v>17.0991</v>
+        <v>17.3102</v>
       </c>
       <c r="G83">
         <v>4.31</v>
@@ -8087,37 +8087,37 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M83">
-        <v>3.43349928</v>
+        <v>3.475888160000001</v>
       </c>
       <c r="N83">
-        <v>-1.650165946666666</v>
+        <v>-1.692554826666667</v>
       </c>
       <c r="O83">
-        <v>-0.2722773812</v>
+        <v>-0.2792715464000001</v>
       </c>
       <c r="P83">
-        <v>-1.377888565466666</v>
+        <v>-1.413283280266667</v>
       </c>
       <c r="Q83">
-        <v>-0.2278885654666662</v>
+        <v>-0.2632832802666669</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5404476057304711</v>
+        <v>0.5679280282710528</v>
       </c>
       <c r="T83">
-        <v>9.641602522791265</v>
+        <v>10.17724710739078</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.08569974128551441</v>
+        <v>0.08465462248934959</v>
       </c>
       <c r="W83">
-        <v>0.1835914919498687</v>
+        <v>0.1838013518041386</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5193923714273601</v>
+        <v>0.5130583181172702</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2529441535681831</v>
+        <v>0.2544941535681832</v>
       </c>
       <c r="C84">
-        <v>-5.143502958463202</v>
+        <v>-5.412955721136083</v>
       </c>
       <c r="D84">
-        <v>7.8566970415368</v>
+        <v>7.798344278863919</v>
       </c>
       <c r="E84">
-        <v>7.900200000000002</v>
+        <v>8.1113</v>
       </c>
       <c r="F84">
-        <v>17.3102</v>
+        <v>17.5213</v>
       </c>
       <c r="G84">
         <v>4.31</v>
@@ -8169,37 +8169,37 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M84">
-        <v>3.475888160000001</v>
+        <v>3.51827704</v>
       </c>
       <c r="N84">
-        <v>-1.692554826666667</v>
+        <v>-1.734943706666667</v>
       </c>
       <c r="O84">
-        <v>-0.2792715464000001</v>
+        <v>-0.2862657116</v>
       </c>
       <c r="P84">
-        <v>-1.413283280266667</v>
+        <v>-1.448677995066667</v>
       </c>
       <c r="Q84">
-        <v>-0.2632832802666669</v>
+        <v>-0.2986779950666665</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.5679280282710528</v>
+        <v>0.5986414416987619</v>
       </c>
       <c r="T84">
-        <v>10.17724710739078</v>
+        <v>10.77590870194318</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.08465462248934959</v>
+        <v>0.08363468727863455</v>
       </c>
       <c r="W84">
-        <v>0.1838013518041386</v>
+        <v>0.1840061547944502</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5130583181172702</v>
+        <v>0.5068768925977851</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2544941535681832</v>
+        <v>0.2560441535681832</v>
       </c>
       <c r="C85">
-        <v>-5.412955721136083</v>
+        <v>-5.681548086213049</v>
       </c>
       <c r="D85">
-        <v>7.798344278863919</v>
+        <v>7.740851913786954</v>
       </c>
       <c r="E85">
-        <v>8.1113</v>
+        <v>8.322400000000002</v>
       </c>
       <c r="F85">
-        <v>17.5213</v>
+        <v>17.7324</v>
       </c>
       <c r="G85">
         <v>4.31</v>
@@ -8251,37 +8251,37 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M85">
-        <v>3.51827704</v>
+        <v>3.56066592</v>
       </c>
       <c r="N85">
-        <v>-1.734943706666667</v>
+        <v>-1.777332586666667</v>
       </c>
       <c r="O85">
-        <v>-0.2862657116</v>
+        <v>-0.2932598768</v>
       </c>
       <c r="P85">
-        <v>-1.448677995066667</v>
+        <v>-1.484072709866667</v>
       </c>
       <c r="Q85">
-        <v>-0.2986779950666665</v>
+        <v>-0.3340727098666667</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5986414416987619</v>
+        <v>0.6331940318049346</v>
       </c>
       <c r="T85">
-        <v>10.77590870194318</v>
+        <v>11.44940299581463</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.08363468727863455</v>
+        <v>0.08263903623960318</v>
       </c>
       <c r="W85">
-        <v>0.1840061547944502</v>
+        <v>0.1842060815230877</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5068768925977851</v>
+        <v>0.5008426438763829</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2560441535681831</v>
+        <v>0.2883847517751391</v>
       </c>
       <c r="C86">
-        <v>-5.681548086213041</v>
+        <v>-6.92463290674036</v>
       </c>
       <c r="D86">
-        <v>7.740851913786957</v>
+        <v>6.708867093259641</v>
       </c>
       <c r="E86">
-        <v>8.322399999999998</v>
+        <v>8.5335</v>
       </c>
       <c r="F86">
-        <v>17.7324</v>
+        <v>17.9435</v>
       </c>
       <c r="G86">
         <v>4.31</v>
@@ -8333,45 +8333,45 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M86">
-        <v>3.56066592</v>
+        <v>4.2310773</v>
       </c>
       <c r="N86">
-        <v>-1.777332586666666</v>
+        <v>-2.447743966666667</v>
       </c>
       <c r="O86">
-        <v>-0.2932598768</v>
+        <v>-0.4038777545</v>
       </c>
       <c r="P86">
-        <v>-1.484072709866667</v>
+        <v>-2.043866212166667</v>
       </c>
       <c r="Q86">
-        <v>-0.3340727098666665</v>
+        <v>-0.8938662121666667</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6331940318049342</v>
+        <v>0.6792909553049699</v>
       </c>
       <c r="T86">
-        <v>11.44940299581462</v>
+        <v>12.34791783498891</v>
       </c>
       <c r="U86">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.0826390362396032</v>
+        <v>0.06954493599065184</v>
       </c>
       <c r="W86">
-        <v>0.1842060815230877</v>
+        <v>0.2194013040934043</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.5008426438763829</v>
+        <v>0.421484460549405</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2883847517751391</v>
+        <v>0.2902847517751391</v>
       </c>
       <c r="C87">
-        <v>-6.92463290674036</v>
+        <v>-7.187870503807833</v>
       </c>
       <c r="D87">
-        <v>6.708867093259641</v>
+        <v>6.656729496192167</v>
       </c>
       <c r="E87">
-        <v>8.5335</v>
+        <v>8.744599999999998</v>
       </c>
       <c r="F87">
-        <v>17.9435</v>
+        <v>18.1546</v>
       </c>
       <c r="G87">
         <v>4.31</v>
@@ -8415,37 +8415,37 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M87">
-        <v>4.2310773</v>
+        <v>4.28085468</v>
       </c>
       <c r="N87">
-        <v>-2.447743966666667</v>
+        <v>-2.497521346666667</v>
       </c>
       <c r="O87">
-        <v>-0.4038777545</v>
+        <v>-0.4120910222</v>
       </c>
       <c r="P87">
-        <v>-2.043866212166667</v>
+        <v>-2.085430324466667</v>
       </c>
       <c r="Q87">
-        <v>-0.8938662121666667</v>
+        <v>-0.9354303244666664</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.6792909553049699</v>
+        <v>0.7245403092553248</v>
       </c>
       <c r="T87">
-        <v>12.34791783498891</v>
+        <v>13.22991196605954</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.06954493599065184</v>
+        <v>0.06873627394424892</v>
       </c>
       <c r="W87">
-        <v>0.2194013040934043</v>
+        <v>0.2195919866039461</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.421484460549405</v>
+        <v>0.4165834784499933</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2902847517751391</v>
+        <v>0.2921847517751391</v>
       </c>
       <c r="C88">
-        <v>-7.187870503807833</v>
+        <v>-7.450303981028485</v>
       </c>
       <c r="D88">
-        <v>6.656729496192167</v>
+        <v>6.605396018971516</v>
       </c>
       <c r="E88">
-        <v>8.744599999999998</v>
+        <v>8.9557</v>
       </c>
       <c r="F88">
-        <v>18.1546</v>
+        <v>18.3657</v>
       </c>
       <c r="G88">
         <v>4.31</v>
@@ -8497,37 +8497,37 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M88">
-        <v>4.28085468</v>
+        <v>4.33063206</v>
       </c>
       <c r="N88">
-        <v>-2.497521346666667</v>
+        <v>-2.547298726666667</v>
       </c>
       <c r="O88">
-        <v>-0.4120910222</v>
+        <v>-0.4203042899000001</v>
       </c>
       <c r="P88">
-        <v>-2.085430324466667</v>
+        <v>-2.126994436766667</v>
       </c>
       <c r="Q88">
-        <v>-0.9354303244666664</v>
+        <v>-0.9769944367666665</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.7245403092553248</v>
+        <v>0.7767511022749651</v>
       </c>
       <c r="T88">
-        <v>13.22991196605954</v>
+        <v>14.24759750191028</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.06873627394424892</v>
+        <v>0.06794620182994721</v>
       </c>
       <c r="W88">
-        <v>0.2195919866039461</v>
+        <v>0.2197782856084984</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4165834784499933</v>
+        <v>0.4117951626057406</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2921847517751391</v>
+        <v>0.2940847517751392</v>
       </c>
       <c r="C89">
-        <v>-7.450303981028485</v>
+        <v>-7.711951798992803</v>
       </c>
       <c r="D89">
-        <v>6.605396018971516</v>
+        <v>6.554848201007196</v>
       </c>
       <c r="E89">
-        <v>8.9557</v>
+        <v>9.166799999999999</v>
       </c>
       <c r="F89">
-        <v>18.3657</v>
+        <v>18.5768</v>
       </c>
       <c r="G89">
         <v>4.31</v>
@@ -8579,37 +8579,37 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M89">
-        <v>4.33063206</v>
+        <v>4.38040944</v>
       </c>
       <c r="N89">
-        <v>-2.547298726666667</v>
+        <v>-2.597076106666667</v>
       </c>
       <c r="O89">
-        <v>-0.4203042899000001</v>
+        <v>-0.4285175576000001</v>
       </c>
       <c r="P89">
-        <v>-2.126994436766667</v>
+        <v>-2.168558549066667</v>
       </c>
       <c r="Q89">
-        <v>-0.9769944367666665</v>
+        <v>-1.018558549066667</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.7767511022749651</v>
+        <v>0.8376636941312123</v>
       </c>
       <c r="T89">
-        <v>14.24759750191028</v>
+        <v>15.43489729373614</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.06794620182994721</v>
+        <v>0.06717408590006144</v>
       </c>
       <c r="W89">
-        <v>0.2197782856084984</v>
+        <v>0.2199603505447655</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4117951626057406</v>
+        <v>0.4071156721215844</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2940847517751392</v>
+        <v>0.2959847517751392</v>
       </c>
       <c r="C90">
-        <v>-7.711951798992803</v>
+        <v>-7.972831857503754</v>
       </c>
       <c r="D90">
-        <v>6.554848201007196</v>
+        <v>6.505068142496246</v>
       </c>
       <c r="E90">
-        <v>9.166799999999999</v>
+        <v>9.3779</v>
       </c>
       <c r="F90">
-        <v>18.5768</v>
+        <v>18.7879</v>
       </c>
       <c r="G90">
         <v>4.31</v>
@@ -8661,37 +8661,37 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M90">
-        <v>4.38040944</v>
+        <v>4.43018682</v>
       </c>
       <c r="N90">
-        <v>-2.597076106666667</v>
+        <v>-2.646853486666667</v>
       </c>
       <c r="O90">
-        <v>-0.4285175576000001</v>
+        <v>-0.4367308253000001</v>
       </c>
       <c r="P90">
-        <v>-2.168558549066667</v>
+        <v>-2.210122661366667</v>
       </c>
       <c r="Q90">
-        <v>-1.018558549066667</v>
+        <v>-1.060122661366667</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.8376636941312123</v>
+        <v>0.9096513026885952</v>
       </c>
       <c r="T90">
-        <v>15.43489729373614</v>
+        <v>16.83806977498487</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.06717408590006144</v>
+        <v>0.06641932088994838</v>
       </c>
       <c r="W90">
-        <v>0.2199603505447655</v>
+        <v>0.2201383241341502</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4071156721215844</v>
+        <v>0.4025413387269599</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2959847517751392</v>
+        <v>0.2978847517751391</v>
       </c>
       <c r="C91">
-        <v>-7.972831857503754</v>
+        <v>-8.232961516710461</v>
       </c>
       <c r="D91">
-        <v>6.505068142496246</v>
+        <v>6.456038483289539</v>
       </c>
       <c r="E91">
-        <v>9.3779</v>
+        <v>9.588999999999999</v>
       </c>
       <c r="F91">
-        <v>18.7879</v>
+        <v>18.999</v>
       </c>
       <c r="G91">
         <v>4.31</v>
@@ -8743,37 +8743,37 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M91">
-        <v>4.43018682</v>
+        <v>4.4799642</v>
       </c>
       <c r="N91">
-        <v>-2.646853486666667</v>
+        <v>-2.696630866666666</v>
       </c>
       <c r="O91">
-        <v>-0.4367308253000001</v>
+        <v>-0.444944093</v>
       </c>
       <c r="P91">
-        <v>-2.210122661366667</v>
+        <v>-2.251686773666666</v>
       </c>
       <c r="Q91">
-        <v>-1.060122661366667</v>
+        <v>-1.101686773666666</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.9096513026885952</v>
+        <v>0.9960364329574549</v>
       </c>
       <c r="T91">
-        <v>16.83806977498487</v>
+        <v>18.52187675248337</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.06641932088994838</v>
+        <v>0.06568132843561564</v>
       </c>
       <c r="W91">
-        <v>0.2201383241341502</v>
+        <v>0.2203123427548818</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4025413387269599</v>
+        <v>0.3980686571855493</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2978847517751391</v>
+        <v>0.2997847517751391</v>
       </c>
       <c r="C92">
-        <v>-8.232961516710461</v>
+        <v>-8.492357617293344</v>
       </c>
       <c r="D92">
-        <v>6.456038483289539</v>
+        <v>6.407742382706658</v>
       </c>
       <c r="E92">
-        <v>9.588999999999999</v>
+        <v>9.8001</v>
       </c>
       <c r="F92">
-        <v>18.999</v>
+        <v>19.2101</v>
       </c>
       <c r="G92">
         <v>4.31</v>
@@ -8825,37 +8825,37 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M92">
-        <v>4.4799642</v>
+        <v>4.52974158</v>
       </c>
       <c r="N92">
-        <v>-2.696630866666666</v>
+        <v>-2.746408246666667</v>
       </c>
       <c r="O92">
-        <v>-0.444944093</v>
+        <v>-0.4531573607000001</v>
       </c>
       <c r="P92">
-        <v>-2.251686773666666</v>
+        <v>-2.293250885966667</v>
       </c>
       <c r="Q92">
-        <v>-1.101686773666666</v>
+        <v>-1.143250885966667</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.9960364329574549</v>
+        <v>1.101618258841617</v>
       </c>
       <c r="T92">
-        <v>18.52187675248337</v>
+        <v>20.57986305831485</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.06568132843561564</v>
+        <v>0.0649595555956638</v>
       </c>
       <c r="W92">
-        <v>0.2203123427548818</v>
+        <v>0.2204825367905425</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3980686571855493</v>
+        <v>0.3936942763373563</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2997847517751391</v>
+        <v>0.3016847517751392</v>
       </c>
       <c r="C93">
-        <v>-8.492357617293344</v>
+        <v>-8.751036499749931</v>
       </c>
       <c r="D93">
-        <v>6.407742382706658</v>
+        <v>6.360163500250068</v>
       </c>
       <c r="E93">
-        <v>9.8001</v>
+        <v>10.0112</v>
       </c>
       <c r="F93">
-        <v>19.2101</v>
+        <v>19.4212</v>
       </c>
       <c r="G93">
         <v>4.31</v>
@@ -8907,37 +8907,37 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M93">
-        <v>4.52974158</v>
+        <v>4.57951896</v>
       </c>
       <c r="N93">
-        <v>-2.746408246666667</v>
+        <v>-2.796185626666666</v>
       </c>
       <c r="O93">
-        <v>-0.4531573607000001</v>
+        <v>-0.4613706284</v>
       </c>
       <c r="P93">
-        <v>-2.293250885966667</v>
+        <v>-2.334814998266666</v>
       </c>
       <c r="Q93">
-        <v>-1.143250885966667</v>
+        <v>-1.184814998266666</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.101618258841617</v>
+        <v>1.233595541196819</v>
       </c>
       <c r="T93">
-        <v>20.57986305831485</v>
+        <v>23.15234594060422</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0649595555956638</v>
+        <v>0.06425347346962398</v>
       </c>
       <c r="W93">
-        <v>0.2204825367905425</v>
+        <v>0.2206490309558627</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3936942763373563</v>
+        <v>0.3894149907249939</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3016847517751392</v>
+        <v>0.3035847517751392</v>
       </c>
       <c r="C94">
-        <v>-8.751036499749931</v>
+        <v>-9.009014022827854</v>
       </c>
       <c r="D94">
-        <v>6.360163500250068</v>
+        <v>6.313285977172147</v>
       </c>
       <c r="E94">
-        <v>10.0112</v>
+        <v>10.2223</v>
       </c>
       <c r="F94">
-        <v>19.4212</v>
+        <v>19.6323</v>
       </c>
       <c r="G94">
         <v>4.31</v>
@@ -8989,37 +8989,37 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M94">
-        <v>4.57951896</v>
+        <v>4.629296340000001</v>
       </c>
       <c r="N94">
-        <v>-2.796185626666666</v>
+        <v>-2.845963006666667</v>
       </c>
       <c r="O94">
-        <v>-0.4613706284</v>
+        <v>-0.4695838961000002</v>
       </c>
       <c r="P94">
-        <v>-2.334814998266666</v>
+        <v>-2.376379110566667</v>
       </c>
       <c r="Q94">
-        <v>-1.184814998266666</v>
+        <v>-1.226379110566667</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.233595541196819</v>
+        <v>1.403280618510651</v>
       </c>
       <c r="T94">
-        <v>23.15234594060422</v>
+        <v>26.45982393211911</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06425347346962398</v>
+        <v>0.06356257590543447</v>
       </c>
       <c r="W94">
-        <v>0.2206490309558627</v>
+        <v>0.2208119446014986</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3894149907249939</v>
+        <v>0.3852277327602088</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3035847517751392</v>
+        <v>0.3054847517751391</v>
       </c>
       <c r="C95">
-        <v>-9.009014022827854</v>
+        <v>-9.266305581148586</v>
       </c>
       <c r="D95">
-        <v>6.313285977172147</v>
+        <v>6.267094418851414</v>
       </c>
       <c r="E95">
-        <v>10.2223</v>
+        <v>10.4334</v>
       </c>
       <c r="F95">
-        <v>19.6323</v>
+        <v>19.8434</v>
       </c>
       <c r="G95">
         <v>4.31</v>
@@ -9071,37 +9071,37 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M95">
-        <v>4.629296340000001</v>
+        <v>4.67907372</v>
       </c>
       <c r="N95">
-        <v>-2.845963006666667</v>
+        <v>-2.895740386666667</v>
       </c>
       <c r="O95">
-        <v>-0.4695838961000002</v>
+        <v>-0.4777971638</v>
       </c>
       <c r="P95">
-        <v>-2.376379110566667</v>
+        <v>-2.417943222866667</v>
       </c>
       <c r="Q95">
-        <v>-1.226379110566667</v>
+        <v>-1.267943222866666</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.403280618510651</v>
+        <v>1.629527388262426</v>
       </c>
       <c r="T95">
-        <v>26.45982393211911</v>
+        <v>30.8697945874723</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06356257590543447</v>
+        <v>0.06288637828941923</v>
       </c>
       <c r="W95">
-        <v>0.2208119446014986</v>
+        <v>0.2209713919993549</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3852277327602088</v>
+        <v>0.3811295653904194</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3054847517751391</v>
+        <v>0.3073847517751391</v>
       </c>
       <c r="C96">
-        <v>-9.266305581148586</v>
+        <v>-9.522926122063197</v>
       </c>
       <c r="D96">
-        <v>6.267094418851414</v>
+        <v>6.221573877936804</v>
       </c>
       <c r="E96">
-        <v>10.4334</v>
+        <v>10.6445</v>
       </c>
       <c r="F96">
-        <v>19.8434</v>
+        <v>20.0545</v>
       </c>
       <c r="G96">
         <v>4.31</v>
@@ -9153,37 +9153,37 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M96">
-        <v>4.67907372</v>
+        <v>4.7288511</v>
       </c>
       <c r="N96">
-        <v>-2.895740386666667</v>
+        <v>-2.945517766666667</v>
       </c>
       <c r="O96">
-        <v>-0.4777971638</v>
+        <v>-0.4860104315000001</v>
       </c>
       <c r="P96">
-        <v>-2.417943222866667</v>
+        <v>-2.459507335166667</v>
       </c>
       <c r="Q96">
-        <v>-1.267943222866666</v>
+        <v>-1.309507335166667</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.629527388262426</v>
+        <v>1.946272865914912</v>
       </c>
       <c r="T96">
-        <v>30.8697945874723</v>
+        <v>37.04375350496678</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06288637828941923</v>
+        <v>0.06222441641268849</v>
       </c>
       <c r="W96">
-        <v>0.2209713919993549</v>
+        <v>0.2211274826098881</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3811295653904194</v>
+        <v>0.377117675228415</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3073847517751391</v>
+        <v>0.3092847517751391</v>
       </c>
       <c r="C97">
-        <v>-9.522926122063197</v>
+        <v>-9.778890161778742</v>
       </c>
       <c r="D97">
-        <v>6.221573877936804</v>
+        <v>6.176709838221261</v>
       </c>
       <c r="E97">
-        <v>10.6445</v>
+        <v>10.8556</v>
       </c>
       <c r="F97">
-        <v>20.0545</v>
+        <v>20.2656</v>
       </c>
       <c r="G97">
         <v>4.31</v>
@@ -9235,37 +9235,37 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M97">
-        <v>4.7288511</v>
+        <v>4.778628480000001</v>
       </c>
       <c r="N97">
-        <v>-2.945517766666667</v>
+        <v>-2.995295146666668</v>
       </c>
       <c r="O97">
-        <v>-0.4860104315000001</v>
+        <v>-0.4942236992000002</v>
       </c>
       <c r="P97">
-        <v>-2.459507335166667</v>
+        <v>-2.501071447466668</v>
       </c>
       <c r="Q97">
-        <v>-1.309507335166667</v>
+        <v>-1.351071447466668</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.946272865914912</v>
+        <v>2.421391082393641</v>
       </c>
       <c r="T97">
-        <v>37.04375350496678</v>
+        <v>46.30469188120849</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06222441641268849</v>
+        <v>0.06157624540838964</v>
       </c>
       <c r="W97">
-        <v>0.2211274826098881</v>
+        <v>0.2212803213327017</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.377117675228415</v>
+        <v>0.3731893661114523</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3092847517751391</v>
+        <v>0.3111847517751392</v>
       </c>
       <c r="C98">
-        <v>-9.778890161778738</v>
+        <v>-10.03421180079198</v>
       </c>
       <c r="D98">
-        <v>6.176709838221261</v>
+        <v>6.132488199208015</v>
       </c>
       <c r="E98">
-        <v>10.8556</v>
+        <v>11.0667</v>
       </c>
       <c r="F98">
-        <v>20.2656</v>
+        <v>20.4767</v>
       </c>
       <c r="G98">
         <v>4.31</v>
@@ -9317,37 +9317,37 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M98">
-        <v>4.77862848</v>
+        <v>4.828405859999999</v>
       </c>
       <c r="N98">
-        <v>-2.995295146666667</v>
+        <v>-3.045072526666666</v>
       </c>
       <c r="O98">
-        <v>-0.4942236992</v>
+        <v>-0.5024369668999999</v>
       </c>
       <c r="P98">
-        <v>-2.501071447466667</v>
+        <v>-2.542635559766666</v>
       </c>
       <c r="Q98">
-        <v>-1.351071447466667</v>
+        <v>-1.392635559766666</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.421391082393635</v>
+        <v>3.213254776524847</v>
       </c>
       <c r="T98">
-        <v>46.30469188120836</v>
+        <v>61.7395891749445</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06157624540838965</v>
+        <v>0.06094143875469493</v>
       </c>
       <c r="W98">
-        <v>0.2212803213327017</v>
+        <v>0.221430008741643</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3731893661114524</v>
+        <v>0.369342053058757</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3111847517751392</v>
+        <v>0.3130847517751391</v>
       </c>
       <c r="C99">
-        <v>-10.03421180079198</v>
+        <v>-10.28890473866484</v>
       </c>
       <c r="D99">
-        <v>6.132488199208015</v>
+        <v>6.088895261335161</v>
       </c>
       <c r="E99">
-        <v>11.0667</v>
+        <v>11.2778</v>
       </c>
       <c r="F99">
-        <v>20.4767</v>
+        <v>20.6878</v>
       </c>
       <c r="G99">
         <v>4.31</v>
@@ -9399,37 +9399,37 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M99">
-        <v>4.828405859999999</v>
+        <v>4.87818324</v>
       </c>
       <c r="N99">
-        <v>-3.045072526666666</v>
+        <v>-3.094849906666667</v>
       </c>
       <c r="O99">
-        <v>-0.5024369668999999</v>
+        <v>-0.5106502346</v>
       </c>
       <c r="P99">
-        <v>-2.542635559766666</v>
+        <v>-2.584199672066667</v>
       </c>
       <c r="Q99">
-        <v>-1.392635559766666</v>
+        <v>-1.434199672066667</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.213254776524847</v>
+        <v>4.79698216478727</v>
       </c>
       <c r="T99">
-        <v>61.7395891749445</v>
+        <v>92.60938376241673</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06094143875469493</v>
+        <v>0.06031958733883067</v>
       </c>
       <c r="W99">
-        <v>0.221430008741643</v>
+        <v>0.2215766413055037</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.369342053058757</v>
+        <v>0.3655732565989738</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3130847517751391</v>
+        <v>0.3149847517751392</v>
       </c>
       <c r="C100">
-        <v>-10.28890473866484</v>
+        <v>-10.54298228817404</v>
       </c>
       <c r="D100">
-        <v>6.088895261335161</v>
+        <v>6.045917711825962</v>
       </c>
       <c r="E100">
-        <v>11.2778</v>
+        <v>11.4889</v>
       </c>
       <c r="F100">
-        <v>20.6878</v>
+        <v>20.8989</v>
       </c>
       <c r="G100">
         <v>4.31</v>
@@ -9481,37 +9481,37 @@
         <v>1.783333333333333</v>
       </c>
       <c r="M100">
-        <v>4.87818324</v>
+        <v>4.927960619999999</v>
       </c>
       <c r="N100">
-        <v>-3.094849906666667</v>
+        <v>-3.144627286666666</v>
       </c>
       <c r="O100">
-        <v>-0.5106502346</v>
+        <v>-0.5188635023</v>
       </c>
       <c r="P100">
-        <v>-2.584199672066667</v>
+        <v>-2.625763784366666</v>
       </c>
       <c r="Q100">
-        <v>-1.434199672066667</v>
+        <v>-1.475763784366666</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.79698216478727</v>
+        <v>9.54816432957454</v>
       </c>
       <c r="T100">
-        <v>92.60938376241673</v>
+        <v>185.2187675248335</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06031958733883067</v>
+        <v>0.05971029857783239</v>
       </c>
       <c r="W100">
-        <v>0.2215766413055037</v>
+        <v>0.2217203115953471</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3655732565989738</v>
+        <v>0.3618805974414084</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3149847517751392</v>
-      </c>
-      <c r="C101">
-        <v>-10.54298228817404</v>
-      </c>
-      <c r="D101">
-        <v>6.045917711825962</v>
-      </c>
-      <c r="E101">
-        <v>11.4889</v>
-      </c>
-      <c r="F101">
-        <v>20.8989</v>
-      </c>
-      <c r="G101">
-        <v>4.31</v>
-      </c>
-      <c r="H101">
-        <v>11.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2.933333333333334</v>
-      </c>
-      <c r="K101">
-        <v>1.15</v>
-      </c>
-      <c r="L101">
-        <v>1.783333333333333</v>
-      </c>
-      <c r="M101">
-        <v>4.927960619999999</v>
-      </c>
-      <c r="N101">
-        <v>-3.144627286666666</v>
-      </c>
-      <c r="O101">
-        <v>-0.5188635023</v>
-      </c>
-      <c r="P101">
-        <v>-2.625763784366666</v>
-      </c>
-      <c r="Q101">
-        <v>-1.475763784366666</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>9.54816432957454</v>
-      </c>
-      <c r="T101">
-        <v>185.2187675248335</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05971029857783239</v>
-      </c>
-      <c r="W101">
-        <v>0.2217203115953471</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3618805974414084</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
